--- a/results/block3_results/label/Normal_1/branches/dataframes/dataset_LCA_B07_Normal_1.xlsx
+++ b/results/block3_results/label/Normal_1/branches/dataframes/dataset_LCA_B07_Normal_1.xlsx
@@ -553,14 +553,14 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>24.44938674448072</v>
+        <v>22.73756640125236</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>12.94918332241907</v>
+        <v>22.74831999714625</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="b">
@@ -606,14 +606,14 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="L3" t="n">
         <v>0.1412437639641267</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>12.94918332241907</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="b">
@@ -659,14 +659,14 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="L4" t="n">
         <v>0.1418041999892184</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>12.94918332241907</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="b">
@@ -712,14 +712,14 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="L5" t="n">
         <v>0.1462774201209379</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>12.94918332241907</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="b">
@@ -765,14 +765,14 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22537890841612</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="L6" t="n">
         <v>0.5960228711038292</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>13.74461230569916</v>
+        <v>25.49191108175334</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="b">
@@ -818,14 +818,14 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92519383307983</v>
+        <v>15.99543613326018</v>
       </c>
       <c r="L7" t="n">
         <v>0.7307865025728671</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>14.01711486461985</v>
+        <v>24.56357073298082</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="b">
@@ -871,14 +871,14 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>15.55123726155539</v>
+        <v>15.62439489880449</v>
       </c>
       <c r="L8" t="n">
         <v>0.9035407319073603</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>14.02341868198291</v>
+        <v>24.56357073298082</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="b">
@@ -924,14 +924,14 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15.50392193361757</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="L9" t="n">
         <v>1.068746663715582</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>14.02341868198291</v>
+        <v>24.2124650153238</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="b">
@@ -977,14 +977,14 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="L10" t="n">
         <v>1.087154158780691</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>14.4136984000467</v>
+        <v>24.2124650153238</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="b">
@@ -1030,14 +1030,14 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="L11" t="n">
         <v>1.087375279641611</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>14.4136984000467</v>
+        <v>24.2124650153238</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="b">
@@ -1083,14 +1083,14 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86969785602394</v>
       </c>
       <c r="L12" t="n">
         <v>1.337704961978807</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>14.4136984000467</v>
+        <v>25.63387442790525</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="b">
@@ -1136,14 +1136,14 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86959415022024</v>
       </c>
       <c r="L13" t="n">
         <v>1.338703830096165</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>14.4136984000467</v>
+        <v>25.63387442790525</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="b">
@@ -1189,14 +1189,14 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>13.96252814601202</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="L14" t="n">
         <v>1.650851799473779</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>14.36056284287022</v>
+        <v>22.33078238648552</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="b">
@@ -1242,14 +1242,14 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.8845474029381</v>
+        <v>12.87463469178007</v>
       </c>
       <c r="L15" t="n">
         <v>2.018967951978974</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>14.32918239439808</v>
+        <v>30.67952774302107</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="b">
@@ -1295,14 +1295,14 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>12.56557511094277</v>
+        <v>12.56213898660848</v>
       </c>
       <c r="L16" t="n">
         <v>2.240089092139182</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>14.33140447444988</v>
+        <v>32.15530502821533</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="b">
@@ -1348,14 +1348,14 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>12.56557511094277</v>
+        <v>12.55954078162074</v>
       </c>
       <c r="L17" t="n">
         <v>2.28202895297122</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>14.33266758623184</v>
+        <v>22.38520659719642</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="b">
@@ -1401,14 +1401,14 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42650727241244</v>
+        <v>12.41804037237105</v>
       </c>
       <c r="L18" t="n">
         <v>2.709109177917012</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>14.69408070284003</v>
+        <v>33.28538885308625</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="b">
@@ -1454,14 +1454,14 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>12.61222121789064</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="L19" t="n">
         <v>3.000430953050925</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>15.39058793177672</v>
+        <v>35.18710400624892</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="b">
@@ -1507,14 +1507,14 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="L20" t="n">
         <v>3.044336945982316</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>15.39058793177672</v>
+        <v>35.18710400624892</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="b">
@@ -1560,14 +1560,14 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="L21" t="n">
         <v>3.044508225464774</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>15.39058793177672</v>
+        <v>35.18710400624892</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="b">
@@ -1613,14 +1613,14 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.88726856229838</v>
+        <v>12.89114719647669</v>
       </c>
       <c r="L22" t="n">
         <v>3.36547051777895</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>15.55279586015389</v>
+        <v>32.25135624930163</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="b">
@@ -1666,14 +1666,14 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>13.08268414389388</v>
+        <v>13.08601325120547</v>
       </c>
       <c r="L23" t="n">
         <v>3.609930529204121</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>16.46410452789935</v>
+        <v>3.642125819453386</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="b">
@@ -1719,14 +1719,14 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.11655963642752</v>
+        <v>13.1112961343127</v>
       </c>
       <c r="L24" t="n">
         <v>3.826624684422638</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>17.37544874440357</v>
+        <v>3.255358354232785</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="b">
@@ -1772,14 +1772,14 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>13.06477406907523</v>
+        <v>13.06050754757873</v>
       </c>
       <c r="L25" t="n">
         <v>3.99764735007134</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>18.99504856873714</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="b">
@@ -1825,14 +1825,14 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
       <c r="L26" t="n">
         <v>4.062919325765148</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>18.99504856873714</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="b">
@@ -1878,14 +1878,14 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
       <c r="L27" t="n">
         <v>4.063188092778018</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>18.99504856873714</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="b">
@@ -1931,14 +1931,14 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.82946633796654</v>
+        <v>12.82287865109407</v>
       </c>
       <c r="L28" t="n">
         <v>4.343621288744651</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>19.35440687995326</v>
+        <v>2.354719534730244</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="b">
@@ -1984,14 +1984,14 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.72199060197538</v>
+        <v>12.71927945377958</v>
       </c>
       <c r="L29" t="n">
         <v>4.701833908505561</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>20.85513318717049</v>
+        <v>2.251765918996991</v>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="b">
@@ -2037,14 +2037,14 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>12.76786570293602</v>
+        <v>12.77031387086443</v>
       </c>
       <c r="L30" t="n">
         <v>4.860241057422114</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>21.57890195439783</v>
+        <v>2.218923888940998</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="b">
@@ -2090,26 +2090,20 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>12.94918332241907</v>
+        <v>12.95485717835137</v>
       </c>
       <c r="L31" t="n">
         <v>5.043919493699776</v>
       </c>
-      <c r="M31" t="n">
-        <v>24.44938674448072</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>22.69930894948986</v>
-      </c>
-      <c r="O31" t="n">
-        <v>23.57434784698529</v>
-      </c>
+        <v>2.218923888940998</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>45.07087361877956</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2149,26 +2143,20 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29520804089071</v>
       </c>
       <c r="L32" t="n">
         <v>5.362812728454265</v>
       </c>
-      <c r="M32" t="n">
-        <v>23.09469567725773</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>26.20186131343188</v>
-      </c>
-      <c r="O32" t="n">
-        <v>24.6482784953448</v>
-      </c>
+        <v>2.301226502659204</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>46.07320490568019</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2208,26 +2196,20 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29710102990174</v>
       </c>
       <c r="L33" t="n">
         <v>5.365503515425706</v>
       </c>
-      <c r="M33" t="n">
-        <v>23.09469567725773</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>26.20186131343188</v>
-      </c>
-      <c r="O33" t="n">
-        <v>24.6482784953448</v>
-      </c>
+        <v>2.301226502659204</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>46.07320490568019</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2267,26 +2249,20 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>13.74461230569916</v>
+        <v>13.75403391875815</v>
       </c>
       <c r="L34" t="n">
         <v>5.628616851355962</v>
       </c>
-      <c r="M34" t="n">
-        <v>16.22537890841612</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>25.66606308824377</v>
-      </c>
-      <c r="O34" t="n">
-        <v>20.94572099832994</v>
-      </c>
+        <v>2.489734249269353</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>34.37985588180492</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2326,26 +2302,20 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>14.01711486461985</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="L35" t="n">
         <v>5.816140910841521</v>
       </c>
-      <c r="M35" t="n">
-        <v>15.92519383307983</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>24.51820949168631</v>
-      </c>
-      <c r="O35" t="n">
-        <v>20.22170166238307</v>
-      </c>
+        <v>2.553315915595588</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>30.68281246234167</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2385,26 +2355,20 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>14.02341868198291</v>
+        <v>14.02914779581027</v>
       </c>
       <c r="L36" t="n">
         <v>5.877887601192315</v>
       </c>
-      <c r="M36" t="n">
-        <v>15.55123726155539</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>24.51820949168631</v>
-      </c>
-      <c r="O36" t="n">
-        <v>20.03472337662085</v>
-      </c>
+        <v>2.553315915595588</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>30.00443071578778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2444,26 +2408,20 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
       <c r="L37" t="n">
         <v>6.284646683358995</v>
       </c>
-      <c r="M37" t="n">
-        <v>14.91383648998964</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>24.17916618470565</v>
-      </c>
-      <c r="O37" t="n">
-        <v>19.54650133734765</v>
-      </c>
+        <v>2.643513293066809</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>26.25944586560697</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2503,26 +2461,20 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
       <c r="L38" t="n">
         <v>6.302376142148187</v>
       </c>
-      <c r="M38" t="n">
-        <v>14.91383648998964</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>24.17916618470565</v>
-      </c>
-      <c r="O38" t="n">
-        <v>19.54650133734765</v>
-      </c>
+        <v>2.643513293066809</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>26.25944586560697</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2562,26 +2514,20 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
       <c r="L39" t="n">
         <v>6.304348322188122</v>
       </c>
-      <c r="M39" t="n">
-        <v>14.91383648998964</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>24.17916618470565</v>
-      </c>
-      <c r="O39" t="n">
-        <v>19.54650133734765</v>
-      </c>
+        <v>2.643513293066809</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>26.25944586560697</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2621,26 +2567,20 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.37286417316269</v>
+        <v>14.37156478609048</v>
       </c>
       <c r="L40" t="n">
         <v>6.432264038688504</v>
       </c>
-      <c r="M40" t="n">
-        <v>14.91383648998964</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>25.5966815762619</v>
-      </c>
-      <c r="O40" t="n">
-        <v>20.25525903312577</v>
-      </c>
+        <v>2.518260643654614</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>29.04132131977636</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2680,26 +2620,20 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>14.36056284287022</v>
+        <v>14.36020323793898</v>
       </c>
       <c r="L41" t="n">
         <v>6.604991549378808</v>
       </c>
-      <c r="M41" t="n">
-        <v>13.96252814601202</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>26.88995911838267</v>
-      </c>
-      <c r="O41" t="n">
-        <v>20.42624363219734</v>
-      </c>
+        <v>2.340871106880618</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>29.69552747214837</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2739,26 +2673,20 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>14.32918239439808</v>
+        <v>14.3290624341717</v>
       </c>
       <c r="L42" t="n">
         <v>6.989456888285787</v>
       </c>
-      <c r="M42" t="n">
-        <v>12.8845474029381</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>30.66588861137356</v>
-      </c>
-      <c r="O42" t="n">
-        <v>21.77521800715583</v>
-      </c>
+        <v>2.216829882042773</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>34.19499915137848</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2798,26 +2726,20 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>14.33140447444988</v>
+        <v>14.3325069672442</v>
       </c>
       <c r="L43" t="n">
         <v>7.248670231984146</v>
       </c>
-      <c r="M43" t="n">
-        <v>12.56557511094277</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>32.12320473761747</v>
-      </c>
-      <c r="O43" t="n">
-        <v>22.34438992428012</v>
-      </c>
+        <v>2.204903626958802</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>35.86128543667724</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2857,26 +2779,20 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>14.33266758623184</v>
+        <v>14.33386682670858</v>
       </c>
       <c r="L44" t="n">
         <v>7.292660146522877</v>
       </c>
-      <c r="M44" t="n">
-        <v>12.56557511094277</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>33.20937179433919</v>
-      </c>
-      <c r="O44" t="n">
-        <v>22.88747345264098</v>
-      </c>
+        <v>2.184586328633258</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>37.37767685066174</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2916,26 +2832,20 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>14.47432312940295</v>
+        <v>14.4778957262455</v>
       </c>
       <c r="L45" t="n">
         <v>7.55112283186556</v>
       </c>
-      <c r="M45" t="n">
-        <v>12.42650727241244</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>29.94731022881903</v>
-      </c>
-      <c r="O45" t="n">
-        <v>21.18690875061573</v>
-      </c>
+        <v>2.122383846363779</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>31.68270416522041</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2975,26 +2885,20 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>14.69408070284003</v>
+        <v>14.70491730440479</v>
       </c>
       <c r="L46" t="n">
         <v>7.785751702669552</v>
       </c>
-      <c r="M46" t="n">
-        <v>12.42650727241244</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>33.25403074862375</v>
-      </c>
-      <c r="O46" t="n">
-        <v>22.84026901051809</v>
-      </c>
+        <v>2.122383846363779</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>35.66590351421294</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3034,26 +2938,20 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>14.90097207929845</v>
+        <v>14.70491730440479</v>
       </c>
       <c r="L47" t="n">
         <v>7.821097692058125</v>
       </c>
-      <c r="M47" t="n">
-        <v>12.42650727241244</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>33.25403074862375</v>
-      </c>
-      <c r="O47" t="n">
-        <v>22.84026901051809</v>
-      </c>
+        <v>2.251000276695078</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>34.76008503911904</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3093,26 +2991,20 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>14.90097207929845</v>
+        <v>14.9139321578258</v>
       </c>
       <c r="L48" t="n">
         <v>7.839976534402345</v>
       </c>
-      <c r="M48" t="n">
-        <v>12.42650727241244</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>35.74430957912962</v>
-      </c>
-      <c r="O48" t="n">
-        <v>24.08540842577103</v>
-      </c>
+        <v>2.251000276695078</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>38.13278223941334</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3152,26 +3044,20 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>15.39058793177672</v>
+        <v>15.39818561758153</v>
       </c>
       <c r="L49" t="n">
         <v>8.092412536401531</v>
       </c>
-      <c r="M49" t="n">
-        <v>12.6149723565889</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>35.22205046464095</v>
-      </c>
-      <c r="O49" t="n">
-        <v>23.91851141061493</v>
-      </c>
+        <v>2.277673647184799</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>35.6540728326996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3211,26 +3097,20 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>15.55279586015389</v>
+        <v>15.55789316181155</v>
       </c>
       <c r="L50" t="n">
         <v>8.184441133185471</v>
       </c>
-      <c r="M50" t="n">
-        <v>12.6149723565889</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>35.22205046464095</v>
-      </c>
-      <c r="O50" t="n">
-        <v>23.91851141061493</v>
-      </c>
+        <v>2.294750488747078</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>34.9759038380138</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3270,26 +3150,20 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>16.46410452789935</v>
+        <v>16.44727977295515</v>
       </c>
       <c r="L51" t="n">
         <v>8.562212621875553</v>
       </c>
-      <c r="M51" t="n">
-        <v>13.08268414389388</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>3.655625202153288</v>
-      </c>
-      <c r="O51" t="n">
-        <v>8.369154673023584</v>
-      </c>
+        <v>2.281309496953031</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>-96.72362587548218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3329,26 +3203,20 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.37544874440357</v>
+        <v>17.34712478394894</v>
       </c>
       <c r="L52" t="n">
         <v>8.789943004433578</v>
       </c>
-      <c r="M52" t="n">
-        <v>13.11655963642752</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>3.264927063259222</v>
-      </c>
-      <c r="O52" t="n">
-        <v>8.190743349843371</v>
-      </c>
+        <v>2.255852802350268</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>-112.1351872749845</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3388,26 +3256,20 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>18.99504856873714</v>
+        <v>19.09058139794423</v>
       </c>
       <c r="L53" t="n">
         <v>9.145765264836118</v>
       </c>
-      <c r="M53" t="n">
-        <v>13.00822550737505</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>2.399377731464309</v>
-      </c>
-      <c r="O53" t="n">
-        <v>7.703801619419681</v>
-      </c>
+        <v>2.300988819494015</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>-146.5672080762643</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3447,26 +3309,20 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>19.35440687995326</v>
+        <v>19.36955181416631</v>
       </c>
       <c r="L54" t="n">
         <v>9.254659275956895</v>
       </c>
-      <c r="M54" t="n">
-        <v>12.82946633796654</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>2.399377731464309</v>
-      </c>
-      <c r="O54" t="n">
-        <v>7.614422034715425</v>
-      </c>
+        <v>2.400491992516112</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>-154.1809055462552</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3506,26 +3362,20 @@
         <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>20.44211148955486</v>
+        <v>20.45962582445294</v>
       </c>
       <c r="L55" t="n">
         <v>9.587414873075637</v>
       </c>
-      <c r="M55" t="n">
-        <v>12.72199060197538</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>2.252836045045917</v>
-      </c>
-      <c r="O55" t="n">
-        <v>7.487413323510647</v>
-      </c>
+        <v>2.433166299696604</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>-173.0196745699368</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3565,26 +3415,20 @@
         <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>20.85513318717049</v>
+        <v>20.87189659295924</v>
       </c>
       <c r="L56" t="n">
         <v>9.640661811858779</v>
       </c>
-      <c r="M56" t="n">
-        <v>12.72199060197538</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
-        <v>2.252836045045917</v>
-      </c>
-      <c r="O56" t="n">
-        <v>7.487413323510647</v>
-      </c>
+        <v>2.433166299696604</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>-178.5358879772926</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3624,26 +3468,20 @@
         <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>21.24417781615288</v>
+        <v>21.25932422424625</v>
       </c>
       <c r="L57" t="n">
         <v>9.77733597393261</v>
       </c>
-      <c r="M57" t="n">
-        <v>12.72199060197538</v>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>2.252836045045917</v>
-      </c>
-      <c r="O57" t="n">
-        <v>7.487413323510647</v>
-      </c>
+        <v>2.328854369026954</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>-183.7318697158828</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3683,26 +3521,20 @@
         <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>21.57890195439783</v>
+        <v>21.5931175452996</v>
       </c>
       <c r="L58" t="n">
         <v>9.909278289958326</v>
       </c>
-      <c r="M58" t="n">
-        <v>12.76786570293602</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
-        <v>2.21979661522538</v>
-      </c>
-      <c r="O58" t="n">
-        <v>7.493831159080701</v>
-      </c>
+        <v>2.328854369026954</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>-187.9555396474266</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3742,25 +3574,25 @@
         <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>22.69930894948986</v>
+        <v>22.74831999714625</v>
       </c>
       <c r="L59" t="n">
         <v>10.05694031425032</v>
       </c>
       <c r="M59" t="n">
-        <v>12.94918332241907</v>
+        <v>22.73756640125236</v>
       </c>
       <c r="N59" t="n">
-        <v>2.21979661522538</v>
+        <v>2.273868442889747</v>
       </c>
       <c r="O59" t="n">
-        <v>7.584489968822226</v>
+        <v>12.50571742207105</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>-199.2858984954894</v>
+        <v>-81.90335851502823</v>
       </c>
     </row>
     <row r="60">
@@ -3801,25 +3633,25 @@
         <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>24.17628142732889</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="L60" t="n">
         <v>10.18455134155159</v>
       </c>
       <c r="M60" t="n">
-        <v>12.94918332241907</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N60" t="n">
-        <v>2.252146836654987</v>
+        <v>2.128291034343583</v>
       </c>
       <c r="O60" t="n">
-        <v>7.600665079537029</v>
+        <v>11.85692654242639</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>-218.0811307212804</v>
+        <v>-104.4482813579799</v>
       </c>
     </row>
     <row r="61">
@@ -3860,25 +3692,25 @@
         <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>24.17628142732889</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="L61" t="n">
         <v>10.20405122176697</v>
       </c>
       <c r="M61" t="n">
-        <v>13.29202663846189</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N61" t="n">
-        <v>2.252146836654987</v>
+        <v>2.128291034343583</v>
       </c>
       <c r="O61" t="n">
-        <v>7.772086737558437</v>
+        <v>11.85692654242639</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>-211.0655123095518</v>
+        <v>-104.4482813579799</v>
       </c>
     </row>
     <row r="62">
@@ -3919,25 +3751,25 @@
         <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>24.17628142732889</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="L62" t="n">
         <v>10.21846951186482</v>
       </c>
       <c r="M62" t="n">
-        <v>13.29202663846189</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N62" t="n">
-        <v>2.252146836654987</v>
+        <v>2.128291034343583</v>
       </c>
       <c r="O62" t="n">
-        <v>7.772086737558437</v>
+        <v>11.85692654242639</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>-211.0655123095518</v>
+        <v>-104.4482813579799</v>
       </c>
     </row>
     <row r="63">
@@ -3978,25 +3810,25 @@
         <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>26.20186131343188</v>
+        <v>26.13980280489467</v>
       </c>
       <c r="L63" t="n">
         <v>10.36393618434353</v>
       </c>
       <c r="M63" t="n">
-        <v>13.29202663846189</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N63" t="n">
-        <v>2.30019580561668</v>
+        <v>2.128291034343583</v>
       </c>
       <c r="O63" t="n">
-        <v>7.796111222039284</v>
+        <v>11.85692654242639</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>-236.0888597812754</v>
+        <v>-120.4601901796505</v>
       </c>
     </row>
     <row r="64">
@@ -4037,25 +3869,25 @@
         <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>26.20186131343188</v>
+        <v>26.13980280489467</v>
       </c>
       <c r="L64" t="n">
         <v>10.36570548024979</v>
       </c>
       <c r="M64" t="n">
-        <v>13.29202663846189</v>
+        <v>21.58556205050919</v>
       </c>
       <c r="N64" t="n">
-        <v>2.30019580561668</v>
+        <v>2.128291034343583</v>
       </c>
       <c r="O64" t="n">
-        <v>7.796111222039284</v>
+        <v>11.85692654242639</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>-236.0888597812754</v>
+        <v>-120.4601901796505</v>
       </c>
     </row>
     <row r="65">
@@ -4096,25 +3928,25 @@
         <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>25.66606308824377</v>
+        <v>26.00010138171323</v>
       </c>
       <c r="L65" t="n">
         <v>10.5403978739916</v>
       </c>
       <c r="M65" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N65" t="n">
-        <v>2.352384292151674</v>
+        <v>1.720801904835842</v>
       </c>
       <c r="O65" t="n">
-        <v>8.048498298925416</v>
+        <v>9.007021207178994</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>-218.892570203693</v>
+        <v>-188.6648180753699</v>
       </c>
     </row>
     <row r="66">
@@ -4155,25 +3987,25 @@
         <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>25.66606308824377</v>
+        <v>25.49191108175334</v>
       </c>
       <c r="L66" t="n">
         <v>10.54251329474666</v>
       </c>
       <c r="M66" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N66" t="n">
-        <v>2.352384292151674</v>
+        <v>1.720801904835842</v>
       </c>
       <c r="O66" t="n">
-        <v>8.048498298925416</v>
+        <v>9.007021207178994</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>-218.892570203693</v>
+        <v>-183.0226608263692</v>
       </c>
     </row>
     <row r="67">
@@ -4214,25 +4046,25 @@
         <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>25.66606308824377</v>
+        <v>25.49191108175334</v>
       </c>
       <c r="L67" t="n">
         <v>10.58575927718809</v>
       </c>
       <c r="M67" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N67" t="n">
-        <v>2.550873196243217</v>
+        <v>1.720801904835842</v>
       </c>
       <c r="O67" t="n">
-        <v>8.147742750971187</v>
+        <v>9.007021207178994</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>-215.0082651441646</v>
+        <v>-183.0226608263692</v>
       </c>
     </row>
     <row r="68">
@@ -4273,25 +4105,25 @@
         <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>25.66606308824377</v>
+        <v>25.49191108175334</v>
       </c>
       <c r="L68" t="n">
         <v>10.58593475326231</v>
       </c>
       <c r="M68" t="n">
-        <v>13.74461230569916</v>
+        <v>16.29324050952215</v>
       </c>
       <c r="N68" t="n">
-        <v>2.550873196243217</v>
+        <v>1.720801904835842</v>
       </c>
       <c r="O68" t="n">
-        <v>8.147742750971187</v>
+        <v>9.007021207178994</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>-215.0082651441646</v>
+        <v>-183.0226608263692</v>
       </c>
     </row>
     <row r="69">
@@ -4332,25 +4164,25 @@
         <v>11</v>
       </c>
       <c r="K69" t="n">
-        <v>24.51820949168631</v>
+        <v>24.56357073298082</v>
       </c>
       <c r="L69" t="n">
         <v>10.80529685030192</v>
       </c>
       <c r="M69" t="n">
-        <v>14.01711486461985</v>
+        <v>15.99543613326018</v>
       </c>
       <c r="N69" t="n">
-        <v>2.550873196243217</v>
+        <v>1.491482234915091</v>
       </c>
       <c r="O69" t="n">
-        <v>8.283994030431533</v>
+        <v>8.743459184087635</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>-195.9708734895008</v>
+        <v>-180.9365288475809</v>
       </c>
     </row>
     <row r="70">
@@ -4391,25 +4223,25 @@
         <v>11</v>
       </c>
       <c r="K70" t="n">
-        <v>24.17916618470565</v>
+        <v>24.2124650153238</v>
       </c>
       <c r="L70" t="n">
         <v>11.11632839768961</v>
       </c>
       <c r="M70" t="n">
-        <v>14.4136984000467</v>
+        <v>15.51994773639756</v>
       </c>
       <c r="N70" t="n">
-        <v>2.653203568705818</v>
+        <v>1.134665013898365</v>
       </c>
       <c r="O70" t="n">
-        <v>8.533450984376259</v>
+        <v>8.327306375147963</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>-183.3456971742715</v>
+        <v>-190.7598678917778</v>
       </c>
     </row>
     <row r="71">
@@ -4450,25 +4282,25 @@
         <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>25.5966815762619</v>
+        <v>25.63387442790525</v>
       </c>
       <c r="L71" t="n">
         <v>11.51234604436302</v>
       </c>
       <c r="M71" t="n">
-        <v>14.37286417316269</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N71" t="n">
-        <v>2.342415712804469</v>
+        <v>0.9478262599968733</v>
       </c>
       <c r="O71" t="n">
-        <v>8.357639942983578</v>
+        <v>7.433237904332331</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>-206.2668618280316</v>
+        <v>-244.8547558657447</v>
       </c>
     </row>
     <row r="72">
@@ -4509,25 +4341,25 @@
         <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>26.88995911838267</v>
+        <v>22.33078238648552</v>
       </c>
       <c r="L72" t="n">
         <v>11.61027833774674</v>
       </c>
       <c r="M72" t="n">
-        <v>14.36056284287022</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N72" t="n">
-        <v>2.342415712804469</v>
+        <v>0.9478262599968733</v>
       </c>
       <c r="O72" t="n">
-        <v>8.351489277837347</v>
+        <v>7.433237904332331</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>-221.9780116313091</v>
+        <v>-200.4179695832206</v>
       </c>
     </row>
     <row r="73">
@@ -4568,25 +4400,25 @@
         <v>11</v>
       </c>
       <c r="K73" t="n">
-        <v>26.88995911838267</v>
+        <v>22.33078238648552</v>
       </c>
       <c r="L73" t="n">
         <v>11.64140345864316</v>
       </c>
       <c r="M73" t="n">
-        <v>14.36056284287022</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N73" t="n">
-        <v>2.342415712804469</v>
+        <v>0.9478262599968733</v>
       </c>
       <c r="O73" t="n">
-        <v>8.351489277837347</v>
+        <v>7.433237904332331</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>-221.9780116313091</v>
+        <v>-200.4179695832206</v>
       </c>
     </row>
     <row r="74">
@@ -4627,25 +4459,25 @@
         <v>11</v>
       </c>
       <c r="K74" t="n">
-        <v>28.52316172484845</v>
+        <v>28.58911449557269</v>
       </c>
       <c r="L74" t="n">
         <v>11.67921135413054</v>
       </c>
       <c r="M74" t="n">
-        <v>14.36056284287022</v>
+        <v>13.91864954866779</v>
       </c>
       <c r="N74" t="n">
-        <v>2.342415712804469</v>
+        <v>0.9478262599968733</v>
       </c>
       <c r="O74" t="n">
-        <v>8.351489277837347</v>
+        <v>7.433237904332331</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>-241.5338363726504</v>
+        <v>-284.6118591053037</v>
       </c>
     </row>
     <row r="75">
@@ -4686,25 +4518,25 @@
         <v>11</v>
       </c>
       <c r="K75" t="n">
-        <v>30.66588861137356</v>
+        <v>30.67952774302107</v>
       </c>
       <c r="L75" t="n">
         <v>11.88384261194657</v>
       </c>
       <c r="M75" t="n">
-        <v>14.32918239439808</v>
+        <v>12.87463469178007</v>
       </c>
       <c r="N75" t="n">
-        <v>2.268576143173112</v>
+        <v>1.047773289556459</v>
       </c>
       <c r="O75" t="n">
-        <v>8.298879268785598</v>
+        <v>6.961203990668263</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>-269.5184327685852</v>
+        <v>-340.7215732242302</v>
       </c>
     </row>
     <row r="76">
@@ -4745,25 +4577,25 @@
         <v>11</v>
       </c>
       <c r="K76" t="n">
-        <v>30.66588861137356</v>
+        <v>30.67952774302107</v>
       </c>
       <c r="L76" t="n">
         <v>11.888704428272</v>
       </c>
       <c r="M76" t="n">
-        <v>14.32918239439808</v>
+        <v>12.87463469178007</v>
       </c>
       <c r="N76" t="n">
-        <v>2.268576143173112</v>
+        <v>1.047773289556459</v>
       </c>
       <c r="O76" t="n">
-        <v>8.298879268785598</v>
+        <v>6.961203990668263</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>-269.5184327685852</v>
+        <v>-340.7215732242302</v>
       </c>
     </row>
     <row r="77">
@@ -4804,25 +4636,25 @@
         <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>32.12320473761747</v>
+        <v>32.15530502821533</v>
       </c>
       <c r="L77" t="n">
         <v>12.19594171132722</v>
       </c>
       <c r="M77" t="n">
-        <v>14.33140447444988</v>
+        <v>12.56213898660848</v>
       </c>
       <c r="N77" t="n">
-        <v>2.205518959400552</v>
+        <v>1.12276815977813</v>
       </c>
       <c r="O77" t="n">
-        <v>8.268461716925215</v>
+        <v>6.842453573193302</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>-288.5027933534788</v>
+        <v>-369.9382273369052</v>
       </c>
     </row>
     <row r="78">
@@ -4863,25 +4695,25 @@
         <v>11</v>
       </c>
       <c r="K78" t="n">
-        <v>33.20937179433919</v>
+        <v>22.38520659719642</v>
       </c>
       <c r="L78" t="n">
         <v>12.3020405419072</v>
       </c>
       <c r="M78" t="n">
-        <v>14.33266758623184</v>
+        <v>12.55954078162074</v>
       </c>
       <c r="N78" t="n">
-        <v>2.185617419654481</v>
+        <v>1.162272388056961</v>
       </c>
       <c r="O78" t="n">
-        <v>8.25914250294316</v>
+        <v>6.860906584838849</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>-302.092248468954</v>
+        <v>-226.2718464446519</v>
       </c>
     </row>
     <row r="79">
@@ -4922,25 +4754,25 @@
         <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>29.94731022881903</v>
+        <v>30.0963262515195</v>
       </c>
       <c r="L79" t="n">
         <v>12.47278233473049</v>
       </c>
       <c r="M79" t="n">
-        <v>14.47432312940295</v>
+        <v>12.55954078162074</v>
       </c>
       <c r="N79" t="n">
-        <v>2.121820681858065</v>
+        <v>1.430509800817653</v>
       </c>
       <c r="O79" t="n">
-        <v>8.298071905630509</v>
+        <v>6.995025291219195</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>-260.8948026649276</v>
+        <v>-330.253287136777</v>
       </c>
     </row>
     <row r="80">
@@ -4981,25 +4813,25 @@
         <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>29.94731022881903</v>
+        <v>30.0963262515195</v>
       </c>
       <c r="L80" t="n">
         <v>12.47627099582546</v>
       </c>
       <c r="M80" t="n">
-        <v>14.47432312940295</v>
+        <v>12.55954078162074</v>
       </c>
       <c r="N80" t="n">
-        <v>2.121820681858065</v>
+        <v>1.430509800817653</v>
       </c>
       <c r="O80" t="n">
-        <v>8.298071905630509</v>
+        <v>6.995025291219195</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>-260.8948026649276</v>
+        <v>-330.253287136777</v>
       </c>
     </row>
     <row r="81">
@@ -5040,25 +4872,25 @@
         <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>33.25403074862375</v>
+        <v>33.28538885308625</v>
       </c>
       <c r="L81" t="n">
         <v>12.7059417867383</v>
       </c>
       <c r="M81" t="n">
-        <v>14.69408070284003</v>
+        <v>12.41804037237105</v>
       </c>
       <c r="N81" t="n">
-        <v>2.121820681858065</v>
+        <v>1.430509800817653</v>
       </c>
       <c r="O81" t="n">
-        <v>8.407950692349047</v>
+        <v>6.924275086594353</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>-295.5069667437965</v>
+        <v>-380.7057552858922</v>
       </c>
     </row>
     <row r="82">
@@ -5099,25 +4931,25 @@
         <v>11</v>
       </c>
       <c r="K82" t="n">
-        <v>35.74430957912962</v>
+        <v>35.18710400624892</v>
       </c>
       <c r="L82" t="n">
         <v>12.9737435271493</v>
       </c>
       <c r="M82" t="n">
-        <v>15.39058793177672</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="N82" t="n">
-        <v>2.249804039781183</v>
+        <v>1.757496593321768</v>
       </c>
       <c r="O82" t="n">
-        <v>8.82019598577895</v>
+        <v>7.184925301683027</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>-305.2552759231334</v>
+        <v>-389.7351402944516</v>
       </c>
     </row>
     <row r="83">
@@ -5158,25 +4990,25 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>35.22205046464095</v>
+        <v>35.1831624682064</v>
       </c>
       <c r="L83" t="n">
         <v>13.12723279690661</v>
       </c>
       <c r="M83" t="n">
-        <v>15.39058793177672</v>
+        <v>12.61235401004429</v>
       </c>
       <c r="N83" t="n">
-        <v>2.276935456485526</v>
+        <v>1.789005990939995</v>
       </c>
       <c r="O83" t="n">
-        <v>8.833761694131121</v>
+        <v>7.20068000049214</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>-298.7208584995155</v>
+        <v>-388.608887852283</v>
       </c>
     </row>
     <row r="84">
@@ -5217,25 +5049,25 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>32.3137282444406</v>
+        <v>32.25135624930163</v>
       </c>
       <c r="L84" t="n">
         <v>13.30444838375335</v>
       </c>
       <c r="M84" t="n">
-        <v>15.55279586015389</v>
+        <v>12.89114719647669</v>
       </c>
       <c r="N84" t="n">
-        <v>2.313323918834337</v>
+        <v>1.778211637127946</v>
       </c>
       <c r="O84" t="n">
-        <v>8.933059889494114</v>
+        <v>7.334679416802317</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>-261.7319109484953</v>
+        <v>-339.7105097111685</v>
       </c>
     </row>
     <row r="85">
@@ -5276,25 +5108,25 @@
         <v>17</v>
       </c>
       <c r="K85" t="n">
-        <v>3.655625202153288</v>
+        <v>3.642125819453386</v>
       </c>
       <c r="L85" t="n">
         <v>13.64691359356472</v>
       </c>
       <c r="M85" t="n">
-        <v>16.46410452789935</v>
+        <v>13.08601325120547</v>
       </c>
       <c r="N85" t="n">
-        <v>2.282193623509603</v>
+        <v>1.751891028671269</v>
       </c>
       <c r="O85" t="n">
-        <v>9.373149075704475</v>
+        <v>7.41895213993837</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>60.99896446084705</v>
+        <v>50.90781351928708</v>
       </c>
     </row>
     <row r="86">
@@ -5335,25 +5167,25 @@
         <v>17</v>
       </c>
       <c r="K86" t="n">
-        <v>3.264927063259222</v>
+        <v>3.255358354232785</v>
       </c>
       <c r="L86" t="n">
         <v>13.70390785727933</v>
       </c>
       <c r="M86" t="n">
-        <v>17.37544874440357</v>
+        <v>13.08601325120547</v>
       </c>
       <c r="N86" t="n">
-        <v>2.261802382317713</v>
+        <v>1.69915042491716</v>
       </c>
       <c r="O86" t="n">
-        <v>9.818625563360644</v>
+        <v>7.392581838061316</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>66.74761612824221</v>
+        <v>55.96452733911845</v>
       </c>
     </row>
     <row r="87">
@@ -5394,25 +5226,25 @@
         <v>17</v>
       </c>
       <c r="K87" t="n">
-        <v>2.399377731464309</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="L87" t="n">
         <v>14.20074848197208</v>
       </c>
       <c r="M87" t="n">
-        <v>19.35440687995326</v>
+        <v>13.00560877247013</v>
       </c>
       <c r="N87" t="n">
-        <v>2.29998581674779</v>
+        <v>1.324849022762463</v>
       </c>
       <c r="O87" t="n">
-        <v>10.82719634835052</v>
+        <v>7.165228897616299</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>77.83934405299813</v>
+        <v>66.53134141884316</v>
       </c>
     </row>
     <row r="88">
@@ -5453,25 +5285,25 @@
         <v>17</v>
       </c>
       <c r="K88" t="n">
-        <v>2.355884347339752</v>
+        <v>2.354719534730244</v>
       </c>
       <c r="L88" t="n">
         <v>14.33586093978781</v>
       </c>
       <c r="M88" t="n">
-        <v>19.35440687995326</v>
+        <v>12.82287865109407</v>
       </c>
       <c r="N88" t="n">
-        <v>2.39899655611404</v>
+        <v>1.195349386467163</v>
       </c>
       <c r="O88" t="n">
-        <v>10.87670171803365</v>
+        <v>7.009114018780616</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>78.34008499622934</v>
+        <v>66.40489042665199</v>
       </c>
     </row>
     <row r="89">
@@ -5512,25 +5344,25 @@
         <v>17</v>
       </c>
       <c r="K89" t="n">
-        <v>2.252836045045917</v>
+        <v>2.251765918996991</v>
       </c>
       <c r="L89" t="n">
         <v>14.74783672958006</v>
       </c>
       <c r="M89" t="n">
-        <v>21.24417781615288</v>
+        <v>12.71927945377958</v>
       </c>
       <c r="N89" t="n">
-        <v>2.43304178777875</v>
+        <v>1.109699562533763</v>
       </c>
       <c r="O89" t="n">
-        <v>11.83860980196582</v>
+        <v>6.91448950815667</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>80.97043417486545</v>
+        <v>67.43409739300785</v>
       </c>
     </row>
     <row r="90">
@@ -5571,25 +5403,25 @@
         <v>17</v>
       </c>
       <c r="K90" t="n">
-        <v>2.21979661522538</v>
+        <v>2.218923888940998</v>
       </c>
       <c r="L90" t="n">
         <v>14.89300737159052</v>
       </c>
       <c r="M90" t="n">
-        <v>21.57890195439783</v>
+        <v>12.77031387086443</v>
       </c>
       <c r="N90" t="n">
-        <v>2.329533845651123</v>
+        <v>1.127925107555623</v>
       </c>
       <c r="O90" t="n">
-        <v>11.95421790002448</v>
+        <v>6.949119489210028</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>81.43085031751986</v>
+        <v>68.06899215956288</v>
       </c>
     </row>
     <row r="91">
@@ -5630,25 +5462,25 @@
         <v>17</v>
       </c>
       <c r="K91" t="n">
-        <v>2.252146836654987</v>
+        <v>2.253347188363659</v>
       </c>
       <c r="L91" t="n">
         <v>15.25813033050765</v>
       </c>
       <c r="M91" t="n">
-        <v>24.17628142732889</v>
+        <v>13.29520804089071</v>
       </c>
       <c r="N91" t="n">
-        <v>2.129964220088542</v>
+        <v>1.078132302319271</v>
       </c>
       <c r="O91" t="n">
-        <v>13.15312282370872</v>
+        <v>7.186670171604991</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>82.87747429381974</v>
+        <v>68.64546257783219</v>
       </c>
     </row>
     <row r="92">
@@ -5689,25 +5521,25 @@
         <v>17</v>
       </c>
       <c r="K92" t="n">
-        <v>2.30019580561668</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="L92" t="n">
         <v>15.37823969282593</v>
       </c>
       <c r="M92" t="n">
-        <v>26.20186131343188</v>
+        <v>13.29710102990174</v>
       </c>
       <c r="N92" t="n">
-        <v>2.129964220088542</v>
+        <v>1.006580384496336</v>
       </c>
       <c r="O92" t="n">
-        <v>14.16591276676021</v>
+        <v>7.151840707199037</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>83.76245962057592</v>
+        <v>67.82329756949437</v>
       </c>
     </row>
     <row r="93">
@@ -5748,25 +5580,25 @@
         <v>17</v>
       </c>
       <c r="K93" t="n">
-        <v>2.352384292151674</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="L93" t="n">
         <v>15.42566087930965</v>
       </c>
       <c r="M93" t="n">
-        <v>26.20186131343188</v>
+        <v>13.29710102990174</v>
       </c>
       <c r="N93" t="n">
-        <v>1.726676601806959</v>
+        <v>1.006580384496336</v>
       </c>
       <c r="O93" t="n">
-        <v>13.96426895761942</v>
+        <v>7.151840707199037</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>83.15426106951251</v>
+        <v>67.82329756949437</v>
       </c>
     </row>
     <row r="94">
@@ -5807,25 +5639,25 @@
         <v>17</v>
       </c>
       <c r="K94" t="n">
-        <v>2.352384292151674</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="L94" t="n">
         <v>15.42603689315034</v>
       </c>
       <c r="M94" t="n">
-        <v>26.20186131343188</v>
+        <v>13.29710102990174</v>
       </c>
       <c r="N94" t="n">
-        <v>1.726676601806959</v>
+        <v>1.006580384496336</v>
       </c>
       <c r="O94" t="n">
-        <v>13.96426895761942</v>
+        <v>7.151840707199037</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>83.15426106951251</v>
+        <v>67.82329756949437</v>
       </c>
     </row>
     <row r="95">
@@ -5866,25 +5698,25 @@
         <v>17</v>
       </c>
       <c r="K95" t="n">
-        <v>2.550873196243217</v>
+        <v>2.489734249269353</v>
       </c>
       <c r="L95" t="n">
         <v>15.72633192208174</v>
       </c>
       <c r="M95" t="n">
-        <v>24.51820949168631</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="N95" t="n">
-        <v>1.604021776767994</v>
+        <v>0.9914318695966965</v>
       </c>
       <c r="O95" t="n">
-        <v>13.06111563422715</v>
+        <v>7.507546319564915</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>80.4697143208919</v>
+        <v>66.83691124514246</v>
       </c>
     </row>
     <row r="96">
@@ -5925,25 +5757,25 @@
         <v>17</v>
       </c>
       <c r="K96" t="n">
-        <v>2.550873196243217</v>
+        <v>2.553315915595588</v>
       </c>
       <c r="L96" t="n">
         <v>15.78965408996961</v>
       </c>
       <c r="M96" t="n">
-        <v>24.51820949168631</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="N96" t="n">
-        <v>1.495663010984039</v>
+        <v>1.070830314670122</v>
       </c>
       <c r="O96" t="n">
-        <v>13.00693625133518</v>
+        <v>7.547245542101627</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>80.3883624325339</v>
+        <v>66.16890359069218</v>
       </c>
     </row>
     <row r="97">
@@ -5984,25 +5816,25 @@
         <v>17</v>
       </c>
       <c r="K97" t="n">
-        <v>2.550873196243217</v>
+        <v>2.553315915595588</v>
       </c>
       <c r="L97" t="n">
         <v>15.81881824268431</v>
       </c>
       <c r="M97" t="n">
-        <v>24.51820949168631</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="N97" t="n">
-        <v>1.495663010984039</v>
+        <v>1.070830314670122</v>
       </c>
       <c r="O97" t="n">
-        <v>13.00693625133518</v>
+        <v>7.547245542101627</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>80.3883624325339</v>
+        <v>66.16890359069218</v>
       </c>
     </row>
     <row r="98">
@@ -6043,25 +5875,25 @@
         <v>17</v>
       </c>
       <c r="K98" t="n">
-        <v>2.550873196243217</v>
+        <v>2.553315915595588</v>
       </c>
       <c r="L98" t="n">
         <v>15.81893668273786</v>
       </c>
       <c r="M98" t="n">
-        <v>24.51820949168631</v>
+        <v>14.02366076953313</v>
       </c>
       <c r="N98" t="n">
-        <v>1.495663010984039</v>
+        <v>1.070830314670122</v>
       </c>
       <c r="O98" t="n">
-        <v>13.00693625133518</v>
+        <v>7.547245542101627</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>80.3883624325339</v>
+        <v>66.16890359069218</v>
       </c>
     </row>
     <row r="99">
@@ -6102,25 +5934,25 @@
         <v>17</v>
       </c>
       <c r="K99" t="n">
-        <v>2.653203568705818</v>
+        <v>2.655054926060676</v>
       </c>
       <c r="L99" t="n">
         <v>16.08787337196535</v>
       </c>
       <c r="M99" t="n">
-        <v>24.17916618470565</v>
+        <v>14.4135370281724</v>
       </c>
       <c r="N99" t="n">
-        <v>1.140911278710099</v>
+        <v>1.189002425173676</v>
       </c>
       <c r="O99" t="n">
-        <v>12.66003873170787</v>
+        <v>7.80126972667304</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>79.04268995591065</v>
+        <v>65.96637446103327</v>
       </c>
     </row>
     <row r="100">
@@ -6161,25 +5993,25 @@
         <v>17</v>
       </c>
       <c r="K100" t="n">
-        <v>2.643804707830325</v>
+        <v>2.643513293066809</v>
       </c>
       <c r="L100" t="n">
         <v>16.21507429298429</v>
       </c>
       <c r="M100" t="n">
-        <v>24.17916618470565</v>
+        <v>14.4135370281724</v>
       </c>
       <c r="N100" t="n">
-        <v>0.9804261502569596</v>
+        <v>1.189002425173676</v>
       </c>
       <c r="O100" t="n">
-        <v>12.57979616748131</v>
+        <v>7.80126972667304</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="n">
-        <v>78.98372380099016</v>
+        <v>66.11432003141144</v>
       </c>
     </row>
     <row r="101">
@@ -6220,25 +6052,25 @@
         <v>17</v>
       </c>
       <c r="K101" t="n">
-        <v>2.418092743267994</v>
+        <v>2.518260643654614</v>
       </c>
       <c r="L101" t="n">
         <v>16.43188164365027</v>
       </c>
       <c r="M101" t="n">
-        <v>25.5966815762619</v>
+        <v>14.37156478609048</v>
       </c>
       <c r="N101" t="n">
-        <v>0.947668382193923</v>
+        <v>1.333565658438912</v>
       </c>
       <c r="O101" t="n">
-        <v>13.27217497922791</v>
+        <v>7.852565222264698</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>81.7807349055259</v>
+        <v>67.93072617194586</v>
       </c>
     </row>
     <row r="102">
@@ -6279,25 +6111,25 @@
         <v>17</v>
       </c>
       <c r="K102" t="n">
-        <v>2.342415712804469</v>
+        <v>2.340871106880618</v>
       </c>
       <c r="L102" t="n">
         <v>16.54263408907606</v>
       </c>
       <c r="M102" t="n">
-        <v>25.5966815762619</v>
+        <v>14.36020323793898</v>
       </c>
       <c r="N102" t="n">
-        <v>0.947668382193923</v>
+        <v>1.311819253749365</v>
       </c>
       <c r="O102" t="n">
-        <v>13.27217497922791</v>
+        <v>7.836011245844172</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>82.35092803952216</v>
+        <v>70.12675156480795</v>
       </c>
     </row>
     <row r="103">
@@ -6338,25 +6170,25 @@
         <v>17</v>
       </c>
       <c r="K103" t="n">
-        <v>2.342415712804469</v>
+        <v>2.340871106880618</v>
       </c>
       <c r="L103" t="n">
         <v>16.61643784380115</v>
       </c>
       <c r="M103" t="n">
-        <v>26.88995911838267</v>
+        <v>14.36020323793898</v>
       </c>
       <c r="N103" t="n">
-        <v>0.947668382193923</v>
+        <v>1.311819253749365</v>
       </c>
       <c r="O103" t="n">
-        <v>13.9188137502883</v>
+        <v>7.836011245844172</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>83.17086675036548</v>
+        <v>70.12675156480795</v>
       </c>
     </row>
     <row r="104">
@@ -6397,25 +6229,25 @@
         <v>17</v>
       </c>
       <c r="K104" t="n">
-        <v>2.268576143173112</v>
+        <v>2.267182618065173</v>
       </c>
       <c r="L104" t="n">
         <v>16.79181464096744</v>
       </c>
       <c r="M104" t="n">
-        <v>30.66588861137356</v>
+        <v>14.36020323793898</v>
       </c>
       <c r="N104" t="n">
-        <v>1.046449695602111</v>
+        <v>1.26813063008406</v>
       </c>
       <c r="O104" t="n">
-        <v>15.85616915348784</v>
+        <v>7.81416693401152</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>85.69278543125216</v>
+        <v>70.98625308096302</v>
       </c>
     </row>
     <row r="105">
@@ -6456,25 +6288,25 @@
         <v>17</v>
       </c>
       <c r="K105" t="n">
-        <v>2.268576143173112</v>
+        <v>2.267182618065173</v>
       </c>
       <c r="L105" t="n">
         <v>16.79660364661579</v>
       </c>
       <c r="M105" t="n">
-        <v>30.66588861137356</v>
+        <v>14.36020323793898</v>
       </c>
       <c r="N105" t="n">
-        <v>1.046449695602111</v>
+        <v>1.26813063008406</v>
       </c>
       <c r="O105" t="n">
-        <v>15.85616915348784</v>
+        <v>7.81416693401152</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="n">
-        <v>85.69278543125216</v>
+        <v>70.98625308096302</v>
       </c>
     </row>
     <row r="106">
@@ -6515,25 +6347,25 @@
         <v>17</v>
       </c>
       <c r="K106" t="n">
-        <v>2.217132450735882</v>
+        <v>2.216829882042773</v>
       </c>
       <c r="L106" t="n">
         <v>16.98309580387754</v>
       </c>
       <c r="M106" t="n">
-        <v>30.66588861137356</v>
+        <v>14.3290624341717</v>
       </c>
       <c r="N106" t="n">
-        <v>1.094491209829949</v>
+        <v>1.167201635602541</v>
       </c>
       <c r="O106" t="n">
-        <v>15.88018991060176</v>
+        <v>7.748132034887119</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>86.03837571705799</v>
+        <v>71.38884737558465</v>
       </c>
     </row>
     <row r="107">
@@ -6574,25 +6406,25 @@
         <v>17</v>
       </c>
       <c r="K107" t="n">
-        <v>2.2116895385719</v>
+        <v>2.211854409627325</v>
       </c>
       <c r="L107" t="n">
         <v>17.06638206997116</v>
       </c>
       <c r="M107" t="n">
-        <v>32.12320473761747</v>
+        <v>14.3290624341717</v>
       </c>
       <c r="N107" t="n">
-        <v>1.094491209829949</v>
+        <v>1.167201635602541</v>
       </c>
       <c r="O107" t="n">
-        <v>16.60884797372371</v>
+        <v>7.748132034887119</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>86.68366678970789</v>
+        <v>71.45306249728166</v>
       </c>
     </row>
     <row r="108">
@@ -6633,25 +6465,25 @@
         <v>17</v>
       </c>
       <c r="K108" t="n">
-        <v>2.205518959400552</v>
+        <v>2.204903626958802</v>
       </c>
       <c r="L108" t="n">
         <v>17.19183213093799</v>
       </c>
       <c r="M108" t="n">
-        <v>32.12320473761747</v>
+        <v>14.3325069672442</v>
       </c>
       <c r="N108" t="n">
-        <v>1.121456763951091</v>
+        <v>1.057776064385731</v>
       </c>
       <c r="O108" t="n">
-        <v>16.62233075078428</v>
+        <v>7.695141515814967</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
       </c>
       <c r="Q108" t="n">
-        <v>86.73159021759635</v>
+        <v>71.34680860089047</v>
       </c>
     </row>
     <row r="109">
@@ -6692,25 +6524,25 @@
         <v>17</v>
       </c>
       <c r="K109" t="n">
-        <v>2.185617419654481</v>
+        <v>2.184586328633258</v>
       </c>
       <c r="L109" t="n">
         <v>17.330665159652</v>
       </c>
       <c r="M109" t="n">
-        <v>33.20937179433919</v>
+        <v>14.33386682670858</v>
       </c>
       <c r="N109" t="n">
-        <v>1.160223779553904</v>
+        <v>1.057776064385731</v>
       </c>
       <c r="O109" t="n">
-        <v>17.18479778694655</v>
+        <v>7.695821445547155</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>87.28168089755086</v>
+        <v>71.61334440916282</v>
       </c>
     </row>
     <row r="110">
@@ -6751,25 +6583,25 @@
         <v>17</v>
       </c>
       <c r="K110" t="n">
-        <v>2.155007908898329</v>
+        <v>2.153742406572132</v>
       </c>
       <c r="L110" t="n">
         <v>17.36539353754666</v>
       </c>
       <c r="M110" t="n">
-        <v>33.20937179433919</v>
+        <v>14.33386682670858</v>
       </c>
       <c r="N110" t="n">
-        <v>1.160223779553904</v>
+        <v>1.057776064385731</v>
       </c>
       <c r="O110" t="n">
-        <v>17.18479778694655</v>
+        <v>7.695821445547155</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>87.45980060041639</v>
+        <v>72.01413232088045</v>
       </c>
     </row>
     <row r="111">
@@ -6810,25 +6642,25 @@
         <v>17</v>
       </c>
       <c r="K111" t="n">
-        <v>2.121820681858065</v>
+        <v>2.122383846363779</v>
       </c>
       <c r="L111" t="n">
         <v>17.55409874082277</v>
       </c>
       <c r="M111" t="n">
-        <v>29.94731022881903</v>
+        <v>14.4778957262455</v>
       </c>
       <c r="N111" t="n">
-        <v>1.427812544501824</v>
+        <v>1.072418604357054</v>
       </c>
       <c r="O111" t="n">
-        <v>15.68756138666043</v>
+        <v>7.775157165301277</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>86.47450276330196</v>
+        <v>72.70301035411238</v>
       </c>
     </row>
     <row r="112">
@@ -6869,25 +6701,25 @@
         <v>17</v>
       </c>
       <c r="K112" t="n">
-        <v>2.121820681858065</v>
+        <v>2.122383846363779</v>
       </c>
       <c r="L112" t="n">
         <v>17.63121806954311</v>
       </c>
       <c r="M112" t="n">
-        <v>33.25403074862375</v>
+        <v>14.4778957262455</v>
       </c>
       <c r="N112" t="n">
-        <v>1.427812544501824</v>
+        <v>1.072418604357054</v>
       </c>
       <c r="O112" t="n">
-        <v>17.34092164656279</v>
+        <v>7.775157165301277</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>87.76408356427446</v>
+        <v>72.70301035411238</v>
       </c>
     </row>
     <row r="113">
@@ -6928,25 +6760,25 @@
         <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>2.249804039781183</v>
+        <v>2.251000276695078</v>
       </c>
       <c r="L113" t="n">
         <v>17.98214091731163</v>
       </c>
       <c r="M113" t="n">
-        <v>35.74430957912962</v>
+        <v>15.39818561758153</v>
       </c>
       <c r="N113" t="n">
-        <v>1.755441115818343</v>
+        <v>1.141152858016309</v>
       </c>
       <c r="O113" t="n">
-        <v>18.74987534747398</v>
+        <v>8.269669237798922</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>88.00096534996815</v>
+        <v>72.78004461887994</v>
       </c>
     </row>
     <row r="114">
@@ -6987,25 +6819,25 @@
         <v>17</v>
       </c>
       <c r="K114" t="n">
-        <v>2.276935456485526</v>
+        <v>2.277673647184799</v>
       </c>
       <c r="L114" t="n">
         <v>18.11152852973939</v>
       </c>
       <c r="M114" t="n">
-        <v>35.22205046464095</v>
+        <v>15.39818561758153</v>
       </c>
       <c r="N114" t="n">
-        <v>1.788673379144996</v>
+        <v>1.141152858016309</v>
       </c>
       <c r="O114" t="n">
-        <v>18.50536192189297</v>
+        <v>8.269669237798922</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>87.69580694451713</v>
+        <v>72.45750003187514</v>
       </c>
     </row>
     <row r="115">
@@ -7046,25 +6878,25 @@
         <v>17</v>
       </c>
       <c r="K115" t="n">
-        <v>2.294309311820022</v>
+        <v>2.294750488747078</v>
       </c>
       <c r="L115" t="n">
         <v>18.17196161878424</v>
       </c>
       <c r="M115" t="n">
-        <v>35.22205046464095</v>
+        <v>15.55789316181155</v>
       </c>
       <c r="N115" t="n">
-        <v>1.788673379144996</v>
+        <v>1.192255315039814</v>
       </c>
       <c r="O115" t="n">
-        <v>18.50536192189297</v>
+        <v>8.375074238425682</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="n">
-        <v>87.60192142415916</v>
+        <v>72.60023704364875</v>
       </c>
     </row>
     <row r="116">
@@ -7105,25 +6937,25 @@
         <v>17</v>
       </c>
       <c r="K116" t="n">
-        <v>2.313323918834337</v>
+        <v>2.313867334222721</v>
       </c>
       <c r="L116" t="n">
         <v>18.248833378264</v>
       </c>
       <c r="M116" t="n">
-        <v>32.3137282444406</v>
+        <v>15.55789316181155</v>
       </c>
       <c r="N116" t="n">
-        <v>1.778274352829337</v>
+        <v>1.192255315039814</v>
       </c>
       <c r="O116" t="n">
-        <v>17.04600129863497</v>
+        <v>8.375074238425682</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>86.42893498418549</v>
+        <v>72.3719782255008</v>
       </c>
     </row>
     <row r="117">
@@ -7164,25 +6996,25 @@
         <v>17</v>
       </c>
       <c r="K117" t="n">
-        <v>2.313323918834337</v>
+        <v>2.313867334222721</v>
       </c>
       <c r="L117" t="n">
         <v>18.33076386432939</v>
       </c>
       <c r="M117" t="n">
-        <v>32.3137282444406</v>
+        <v>15.55789316181155</v>
       </c>
       <c r="N117" t="n">
-        <v>1.778274352829337</v>
+        <v>1.192255315039814</v>
       </c>
       <c r="O117" t="n">
-        <v>17.04600129863497</v>
+        <v>8.375074238425682</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>86.42893498418549</v>
+        <v>72.3719782255008</v>
       </c>
     </row>
     <row r="118">
@@ -7223,25 +7055,25 @@
         <v>17</v>
       </c>
       <c r="K118" t="n">
-        <v>2.319676220724453</v>
+        <v>2.319466391467313</v>
       </c>
       <c r="L118" t="n">
         <v>18.41488261688433</v>
       </c>
       <c r="M118" t="n">
-        <v>32.3137282444406</v>
+        <v>16.44727977295515</v>
       </c>
       <c r="N118" t="n">
-        <v>1.778274352829337</v>
+        <v>1.487461797283134</v>
       </c>
       <c r="O118" t="n">
-        <v>17.04600129863497</v>
+        <v>8.967370785119142</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>86.39166934176986</v>
+        <v>74.13437620627509</v>
       </c>
     </row>
     <row r="119">
@@ -7282,25 +7114,25 @@
         <v>17</v>
       </c>
       <c r="K119" t="n">
-        <v>2.282193623509603</v>
+        <v>2.281309496953031</v>
       </c>
       <c r="L119" t="n">
         <v>18.60047075269025</v>
       </c>
       <c r="M119" t="n">
-        <v>3.655625202153288</v>
+        <v>16.44727977295515</v>
       </c>
       <c r="N119" t="n">
-        <v>1.752865128020558</v>
+        <v>1.548748605141129</v>
       </c>
       <c r="O119" t="n">
-        <v>2.704245165086923</v>
+        <v>8.998014189048138</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>15.60699995052977</v>
+        <v>74.64652256572668</v>
       </c>
     </row>
     <row r="120">
@@ -7341,25 +7173,25 @@
         <v>17</v>
       </c>
       <c r="K120" t="n">
-        <v>2.261802382317713</v>
+        <v>2.26132578279934</v>
       </c>
       <c r="L120" t="n">
         <v>18.71400462352171</v>
       </c>
       <c r="M120" t="n">
-        <v>3.264927063259222</v>
+        <v>17.34712478394894</v>
       </c>
       <c r="N120" t="n">
-        <v>1.701855296213878</v>
+        <v>1.548748605141129</v>
       </c>
       <c r="O120" t="n">
-        <v>2.483391179736549</v>
+        <v>9.447936694545033</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="n">
-        <v>8.922830975116202</v>
+        <v>76.06540077575917</v>
       </c>
     </row>
     <row r="121">
@@ -7400,25 +7232,25 @@
         <v>17</v>
       </c>
       <c r="K121" t="n">
-        <v>2.255876719294342</v>
+        <v>2.255852802350268</v>
       </c>
       <c r="L121" t="n">
         <v>18.75800626736779</v>
       </c>
       <c r="M121" t="n">
-        <v>3.264927063259222</v>
+        <v>17.34712478394894</v>
       </c>
       <c r="N121" t="n">
-        <v>1.701855296213878</v>
+        <v>1.548748605141129</v>
       </c>
       <c r="O121" t="n">
-        <v>2.483391179736549</v>
+        <v>9.447936694545033</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="n">
-        <v>9.161442719883672</v>
+        <v>76.1233285606927</v>
       </c>
     </row>
     <row r="122">
@@ -7459,25 +7291,25 @@
         <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>2.255876719294342</v>
+        <v>2.255852802350268</v>
       </c>
       <c r="L122" t="n">
         <v>18.82925571688283</v>
       </c>
       <c r="M122" t="n">
-        <v>3.264927063259222</v>
+        <v>17.34712478394894</v>
       </c>
       <c r="N122" t="n">
-        <v>1.701855296213878</v>
+        <v>1.844802313212991</v>
       </c>
       <c r="O122" t="n">
-        <v>2.483391179736549</v>
+        <v>9.595963548580965</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>9.161442719883672</v>
+        <v>76.49164890081455</v>
       </c>
     </row>
     <row r="123">
@@ -7518,25 +7350,25 @@
         <v>17</v>
       </c>
       <c r="K123" t="n">
-        <v>2.278145012965538</v>
+        <v>2.278718840385056</v>
       </c>
       <c r="L123" t="n">
         <v>18.98023853707771</v>
       </c>
       <c r="M123" t="n">
-        <v>2.399377731464309</v>
+        <v>19.09058139794423</v>
       </c>
       <c r="N123" t="n">
-        <v>1.39792805562581</v>
+        <v>1.844802313212991</v>
       </c>
       <c r="O123" t="n">
-        <v>1.89865289354506</v>
+        <v>10.46769185557861</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
       </c>
       <c r="Q123" t="n">
-        <v>-19.98744060647713</v>
+        <v>78.23093312428139</v>
       </c>
     </row>
     <row r="124">
@@ -7577,25 +7409,25 @@
         <v>17</v>
       </c>
       <c r="K124" t="n">
-        <v>2.278145012965538</v>
+        <v>2.278718840385056</v>
       </c>
       <c r="L124" t="n">
         <v>18.99239945930674</v>
       </c>
       <c r="M124" t="n">
-        <v>2.399377731464309</v>
+        <v>19.09058139794423</v>
       </c>
       <c r="N124" t="n">
-        <v>1.39792805562581</v>
+        <v>1.844802313212991</v>
       </c>
       <c r="O124" t="n">
-        <v>1.89865289354506</v>
+        <v>10.46769185557861</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>-19.98744060647713</v>
+        <v>78.23093312428139</v>
       </c>
     </row>
     <row r="125">
@@ -7636,25 +7468,25 @@
         <v>17</v>
       </c>
       <c r="K125" t="n">
-        <v>2.29998581674779</v>
+        <v>2.300988819494015</v>
       </c>
       <c r="L125" t="n">
         <v>19.07795126350968</v>
       </c>
       <c r="M125" t="n">
-        <v>2.399377731464309</v>
+        <v>19.09058139794423</v>
       </c>
       <c r="N125" t="n">
-        <v>1.39792805562581</v>
+        <v>1.84114621481359</v>
       </c>
       <c r="O125" t="n">
-        <v>1.89865289354506</v>
+        <v>10.46586380637891</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>-21.13777218401325</v>
+        <v>78.01434394654009</v>
       </c>
     </row>
     <row r="126">
@@ -7695,25 +7527,25 @@
         <v>17</v>
       </c>
       <c r="K126" t="n">
-        <v>2.39899655611404</v>
+        <v>2.400491992516112</v>
       </c>
       <c r="L126" t="n">
         <v>19.37826324437647</v>
       </c>
       <c r="M126" t="n">
-        <v>2.355884347339752</v>
+        <v>19.36955181416631</v>
       </c>
       <c r="N126" t="n">
-        <v>1.1971891976014</v>
+        <v>1.642536369273613</v>
       </c>
       <c r="O126" t="n">
-        <v>1.776536772470576</v>
+        <v>10.50604409171996</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>-35.03782152383075</v>
+        <v>77.15132383264989</v>
       </c>
     </row>
     <row r="127">
@@ -7754,25 +7586,25 @@
         <v>17</v>
       </c>
       <c r="K127" t="n">
-        <v>2.426003596047259</v>
+        <v>2.426433234651199</v>
       </c>
       <c r="L127" t="n">
         <v>19.47187403992983</v>
       </c>
       <c r="M127" t="n">
-        <v>2.355884347339752</v>
+        <v>20.45962582445294</v>
       </c>
       <c r="N127" t="n">
-        <v>1.1971891976014</v>
+        <v>1.554274485292735</v>
       </c>
       <c r="O127" t="n">
-        <v>1.776536772470576</v>
+        <v>11.00695015487284</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>-36.55802872425144</v>
+        <v>77.95544450996715</v>
       </c>
     </row>
     <row r="128">
@@ -7813,25 +7645,25 @@
         <v>17</v>
       </c>
       <c r="K128" t="n">
-        <v>2.43304178777875</v>
+        <v>2.433166299696604</v>
       </c>
       <c r="L128" t="n">
         <v>19.63448847858553</v>
       </c>
       <c r="M128" t="n">
-        <v>2.252836045045917</v>
+        <v>20.87189659295924</v>
       </c>
       <c r="N128" t="n">
-        <v>1.110326020176739</v>
+        <v>1.554274485292735</v>
       </c>
       <c r="O128" t="n">
-        <v>1.681581032611328</v>
+        <v>11.21308553912598</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>-44.68775162148913</v>
+        <v>78.30065336426337</v>
       </c>
     </row>
     <row r="129">
@@ -7872,25 +7704,25 @@
         <v>17</v>
       </c>
       <c r="K129" t="n">
-        <v>2.329533845651123</v>
+        <v>2.328854369026954</v>
       </c>
       <c r="L129" t="n">
         <v>19.88189280459844</v>
       </c>
       <c r="M129" t="n">
-        <v>2.21979661522538</v>
+        <v>21.5931175452996</v>
       </c>
       <c r="N129" t="n">
-        <v>1.127592304758405</v>
+        <v>1.19907899481458</v>
       </c>
       <c r="O129" t="n">
-        <v>1.673694459991892</v>
+        <v>11.39609827005709</v>
       </c>
       <c r="P129" t="b">
         <v>1</v>
       </c>
       <c r="Q129" t="n">
-        <v>-39.1851321335202</v>
+        <v>79.56445869595605</v>
       </c>
     </row>
     <row r="130">
@@ -7931,25 +7763,25 @@
         <v>17</v>
       </c>
       <c r="K130" t="n">
-        <v>2.329533845651123</v>
+        <v>2.328854369026954</v>
       </c>
       <c r="L130" t="n">
         <v>19.95044815676346</v>
       </c>
       <c r="M130" t="n">
-        <v>2.21979661522538</v>
+        <v>21.5931175452996</v>
       </c>
       <c r="N130" t="n">
-        <v>1.129235734728124</v>
+        <v>1.19907899481458</v>
       </c>
       <c r="O130" t="n">
-        <v>1.674516174976752</v>
+        <v>11.39609827005709</v>
       </c>
       <c r="P130" t="b">
         <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>-39.11683150408891</v>
+        <v>79.56445869595605</v>
       </c>
     </row>
     <row r="131">
@@ -7990,25 +7822,25 @@
         <v>17</v>
       </c>
       <c r="K131" t="n">
-        <v>2.329533845651123</v>
+        <v>2.328854369026954</v>
       </c>
       <c r="L131" t="n">
         <v>19.95127990074444</v>
       </c>
       <c r="M131" t="n">
-        <v>2.21979661522538</v>
+        <v>21.5931175452996</v>
       </c>
       <c r="N131" t="n">
-        <v>1.129235734728124</v>
+        <v>1.19907899481458</v>
       </c>
       <c r="O131" t="n">
-        <v>1.674516174976752</v>
+        <v>11.39609827005709</v>
       </c>
       <c r="P131" t="b">
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>-39.11683150408891</v>
+        <v>79.56445869595605</v>
       </c>
     </row>
     <row r="132">
@@ -8049,25 +7881,25 @@
         <v>17</v>
       </c>
       <c r="K132" t="n">
-        <v>2.275503708438266</v>
+        <v>2.273868442889747</v>
       </c>
       <c r="L132" t="n">
         <v>20.01974909211556</v>
       </c>
       <c r="M132" t="n">
-        <v>2.21979661522538</v>
+        <v>22.74831999714625</v>
       </c>
       <c r="N132" t="n">
-        <v>1.129235734728124</v>
+        <v>1.19907899481458</v>
       </c>
       <c r="O132" t="n">
-        <v>1.674516174976752</v>
+        <v>11.97369949598042</v>
       </c>
       <c r="P132" t="b">
         <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>-35.890219661202</v>
+        <v>81.00947461013961</v>
       </c>
     </row>
     <row r="133">
@@ -8108,25 +7940,25 @@
         <v>17</v>
       </c>
       <c r="K133" t="n">
-        <v>2.129964220088542</v>
+        <v>2.128291034343583</v>
       </c>
       <c r="L133" t="n">
         <v>20.21068082888961</v>
       </c>
       <c r="M133" t="n">
-        <v>2.252146836654987</v>
+        <v>24.24128253786889</v>
       </c>
       <c r="N133" t="n">
-        <v>1.07931209195279</v>
+        <v>0.8651156562453568</v>
       </c>
       <c r="O133" t="n">
-        <v>1.665729464303888</v>
+        <v>12.55319909705712</v>
       </c>
       <c r="P133" t="b">
         <v>1</v>
       </c>
       <c r="Q133" t="n">
-        <v>-27.86975710840643</v>
+        <v>83.04582745889434</v>
       </c>
     </row>
     <row r="134">
@@ -8167,25 +7999,25 @@
         <v>17</v>
       </c>
       <c r="K134" t="n">
-        <v>1.726676601806959</v>
+        <v>1.720801904835842</v>
       </c>
       <c r="L134" t="n">
         <v>20.57515762758737</v>
       </c>
       <c r="M134" t="n">
-        <v>2.352384292151674</v>
+        <v>25.49191108175334</v>
       </c>
       <c r="N134" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.6183973554889365</v>
       </c>
       <c r="O134" t="n">
-        <v>1.671919298661189</v>
+        <v>13.05515421862114</v>
       </c>
       <c r="P134" t="b">
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>-3.275116400033018</v>
+        <v>86.81898447142518</v>
       </c>
     </row>
     <row r="135">
@@ -8226,25 +8058,25 @@
         <v>17</v>
       </c>
       <c r="K135" t="n">
-        <v>1.726676601806959</v>
+        <v>1.720801904835842</v>
       </c>
       <c r="L135" t="n">
         <v>20.61932831476618</v>
       </c>
       <c r="M135" t="n">
-        <v>2.550873196243217</v>
+        <v>25.49191108175334</v>
       </c>
       <c r="N135" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.6183973554889365</v>
       </c>
       <c r="O135" t="n">
-        <v>1.77116375070696</v>
+        <v>13.05515421862114</v>
       </c>
       <c r="P135" t="b">
         <v>1</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.511746803887815</v>
+        <v>86.81898447142518</v>
       </c>
     </row>
     <row r="136">
@@ -8285,25 +8117,25 @@
         <v>17</v>
       </c>
       <c r="K136" t="n">
-        <v>1.604021776767994</v>
+        <v>1.598275715985946</v>
       </c>
       <c r="L136" t="n">
         <v>20.75508432726687</v>
       </c>
       <c r="M136" t="n">
-        <v>2.550873196243217</v>
+        <v>24.56357073298082</v>
       </c>
       <c r="N136" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.5382015538476752</v>
       </c>
       <c r="O136" t="n">
-        <v>1.77116375070696</v>
+        <v>12.55088614341425</v>
       </c>
       <c r="P136" t="b">
         <v>1</v>
       </c>
       <c r="Q136" t="n">
-        <v>9.436844779160126</v>
+        <v>87.2656344920745</v>
       </c>
     </row>
     <row r="137">
@@ -8344,25 +8176,25 @@
         <v>17</v>
       </c>
       <c r="K137" t="n">
-        <v>1.495663010984039</v>
+        <v>1.491482234915091</v>
       </c>
       <c r="L137" t="n">
         <v>20.822539038168</v>
       </c>
       <c r="M137" t="n">
-        <v>2.550873196243217</v>
+        <v>24.56357073298082</v>
       </c>
       <c r="N137" t="n">
-        <v>1.06923049452409</v>
+        <v>0.5382015538476752</v>
       </c>
       <c r="O137" t="n">
-        <v>1.810051845383653</v>
+        <v>12.55088614341425</v>
       </c>
       <c r="P137" t="b">
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>17.36905134521036</v>
+        <v>88.11651848425295</v>
       </c>
     </row>
     <row r="138">
@@ -8403,25 +8235,25 @@
         <v>17</v>
       </c>
       <c r="K138" t="n">
-        <v>1.495663010984039</v>
+        <v>1.491482234915091</v>
       </c>
       <c r="L138" t="n">
         <v>20.84843572073983</v>
       </c>
       <c r="M138" t="n">
-        <v>2.550873196243217</v>
+        <v>24.56357073298082</v>
       </c>
       <c r="N138" t="n">
-        <v>1.06923049452409</v>
+        <v>0.5382015538476752</v>
       </c>
       <c r="O138" t="n">
-        <v>1.810051845383653</v>
+        <v>12.55088614341425</v>
       </c>
       <c r="P138" t="b">
         <v>1</v>
       </c>
       <c r="Q138" t="n">
-        <v>17.36905134521036</v>
+        <v>88.11651848425295</v>
       </c>
     </row>
     <row r="139">
@@ -8462,25 +8294,25 @@
         <v>17</v>
       </c>
       <c r="K139" t="n">
-        <v>1.140911278710099</v>
+        <v>1.134665013898365</v>
       </c>
       <c r="L139" t="n">
         <v>21.08814339166512</v>
       </c>
       <c r="M139" t="n">
-        <v>2.653203568705818</v>
+        <v>24.2124650153238</v>
       </c>
       <c r="N139" t="n">
-        <v>1.187175472566269</v>
+        <v>0.4521278570745698</v>
       </c>
       <c r="O139" t="n">
-        <v>1.920189520636044</v>
+        <v>12.33229643619919</v>
       </c>
       <c r="P139" t="b">
         <v>1</v>
       </c>
       <c r="Q139" t="n">
-        <v>40.58340250017697</v>
+        <v>90.79923986770409</v>
       </c>
     </row>
     <row r="140">
@@ -8521,25 +8353,25 @@
         <v>17</v>
       </c>
       <c r="K140" t="n">
-        <v>0.9804261502569596</v>
+        <v>0.9788732688213817</v>
       </c>
       <c r="L140" t="n">
         <v>21.2947184673504</v>
       </c>
       <c r="M140" t="n">
-        <v>2.643804707830325</v>
+        <v>24.2124650153238</v>
       </c>
       <c r="N140" t="n">
-        <v>1.187175472566269</v>
+        <v>0.4521278570745698</v>
       </c>
       <c r="O140" t="n">
-        <v>1.915490090198297</v>
+        <v>12.33229643619919</v>
       </c>
       <c r="P140" t="b">
         <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>48.81591111988144</v>
+        <v>92.06252238676262</v>
       </c>
     </row>
     <row r="141">
@@ -8580,25 +8412,25 @@
         <v>17</v>
       </c>
       <c r="K141" t="n">
-        <v>0.947668382193923</v>
+        <v>0.9478262599968733</v>
       </c>
       <c r="L141" t="n">
         <v>21.56596276403852</v>
       </c>
       <c r="M141" t="n">
-        <v>2.342415712804469</v>
+        <v>22.33078238648552</v>
       </c>
       <c r="N141" t="n">
-        <v>1.312922373703677</v>
+        <v>0.4038849076641726</v>
       </c>
       <c r="O141" t="n">
-        <v>1.827669043254073</v>
+        <v>11.36733364707485</v>
       </c>
       <c r="P141" t="b">
         <v>1</v>
       </c>
       <c r="Q141" t="n">
-        <v>48.14879719652924</v>
+        <v>91.66184182303141</v>
       </c>
     </row>
     <row r="142">
@@ -8639,25 +8471,25 @@
         <v>17</v>
       </c>
       <c r="K142" t="n">
-        <v>1.046449695602111</v>
+        <v>1.047773289556459</v>
       </c>
       <c r="L142" t="n">
         <v>21.8256816951343</v>
       </c>
       <c r="M142" t="n">
-        <v>2.268576143173112</v>
+        <v>30.67952774302107</v>
       </c>
       <c r="N142" t="n">
-        <v>1.269293198848958</v>
+        <v>0.4707722187943567</v>
       </c>
       <c r="O142" t="n">
-        <v>1.768934671011035</v>
+        <v>15.57514998090771</v>
       </c>
       <c r="P142" t="b">
         <v>1</v>
       </c>
       <c r="Q142" t="n">
-        <v>40.84294277504251</v>
+        <v>93.27278844286676</v>
       </c>
     </row>
     <row r="143">
@@ -8698,25 +8530,25 @@
         <v>17</v>
       </c>
       <c r="K143" t="n">
-        <v>1.046449695602111</v>
+        <v>1.047773289556459</v>
       </c>
       <c r="L143" t="n">
         <v>21.83854472082154</v>
       </c>
       <c r="M143" t="n">
-        <v>2.268576143173112</v>
+        <v>30.67952774302107</v>
       </c>
       <c r="N143" t="n">
-        <v>1.167607646918589</v>
+        <v>0.4707722187943567</v>
       </c>
       <c r="O143" t="n">
-        <v>1.718091895045851</v>
+        <v>15.57514998090771</v>
       </c>
       <c r="P143" t="b">
         <v>1</v>
       </c>
       <c r="Q143" t="n">
-        <v>39.09233268490654</v>
+        <v>93.27278844286676</v>
       </c>
     </row>
     <row r="144">
@@ -8757,25 +8589,25 @@
         <v>17</v>
       </c>
       <c r="K144" t="n">
-        <v>1.094491209829949</v>
+        <v>1.095635378655122</v>
       </c>
       <c r="L144" t="n">
         <v>22.01827709881056</v>
       </c>
       <c r="M144" t="n">
-        <v>2.217132450735882</v>
+        <v>30.67952774302107</v>
       </c>
       <c r="N144" t="n">
-        <v>1.167607646918589</v>
+        <v>0.4707722187943567</v>
       </c>
       <c r="O144" t="n">
-        <v>1.692370048827236</v>
+        <v>15.57514998090771</v>
       </c>
       <c r="P144" t="b">
         <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>35.32790239413652</v>
+        <v>92.9654906694435</v>
       </c>
     </row>
     <row r="145">
@@ -8816,25 +8648,25 @@
         <v>17</v>
       </c>
       <c r="K145" t="n">
-        <v>1.121456763951091</v>
+        <v>1.12276815977813</v>
       </c>
       <c r="L145" t="n">
         <v>22.14510989561685</v>
       </c>
       <c r="M145" t="n">
-        <v>2.205518959400552</v>
+        <v>32.15530502821533</v>
       </c>
       <c r="N145" t="n">
-        <v>1.167607646918589</v>
+        <v>0.6714789403316066</v>
       </c>
       <c r="O145" t="n">
-        <v>1.686563303159571</v>
+        <v>16.41339198427347</v>
       </c>
       <c r="P145" t="b">
         <v>1</v>
       </c>
       <c r="Q145" t="n">
-        <v>33.5063936319391</v>
+        <v>93.15943858006979</v>
       </c>
     </row>
     <row r="146">
@@ -8875,25 +8707,25 @@
         <v>17</v>
       </c>
       <c r="K146" t="n">
-        <v>1.160223779553904</v>
+        <v>1.162272388056961</v>
       </c>
       <c r="L146" t="n">
         <v>22.25452705139286</v>
       </c>
       <c r="M146" t="n">
-        <v>2.205518959400552</v>
+        <v>22.38520659719642</v>
       </c>
       <c r="N146" t="n">
-        <v>1.058335978988722</v>
+        <v>0.7188562559589849</v>
       </c>
       <c r="O146" t="n">
-        <v>1.631927469194637</v>
+        <v>11.5520314265777</v>
       </c>
       <c r="P146" t="b">
         <v>1</v>
       </c>
       <c r="Q146" t="n">
-        <v>28.90469696386204</v>
+        <v>89.93880517514066</v>
       </c>
     </row>
     <row r="147">
@@ -8934,25 +8766,25 @@
         <v>17</v>
       </c>
       <c r="K147" t="n">
-        <v>1.427812544501824</v>
+        <v>1.430509800817653</v>
       </c>
       <c r="L147" t="n">
         <v>22.58408123718562</v>
       </c>
       <c r="M147" t="n">
-        <v>2.121820681858065</v>
+        <v>30.0963262515195</v>
       </c>
       <c r="N147" t="n">
-        <v>1.072186129913543</v>
+        <v>0.9040520603033265</v>
       </c>
       <c r="O147" t="n">
-        <v>1.597003405885804</v>
+        <v>15.50018915591141</v>
       </c>
       <c r="P147" t="b">
         <v>1</v>
       </c>
       <c r="Q147" t="n">
-        <v>10.59427054196763</v>
+        <v>90.77101713773544</v>
       </c>
     </row>
     <row r="148">
@@ -8993,25 +8825,25 @@
         <v>17</v>
       </c>
       <c r="K148" t="n">
-        <v>1.427812544501824</v>
+        <v>1.430509800817653</v>
       </c>
       <c r="L148" t="n">
         <v>22.66676284394356</v>
       </c>
       <c r="M148" t="n">
-        <v>2.121820681858065</v>
+        <v>33.28538885308625</v>
       </c>
       <c r="N148" t="n">
-        <v>1.104115376478233</v>
+        <v>0.9040520603033265</v>
       </c>
       <c r="O148" t="n">
-        <v>1.612968029168149</v>
+        <v>17.09472045669479</v>
       </c>
       <c r="P148" t="b">
         <v>1</v>
       </c>
       <c r="Q148" t="n">
-        <v>11.47917883789763</v>
+        <v>91.63186198662041</v>
       </c>
     </row>
     <row r="149">
@@ -9052,25 +8884,25 @@
         <v>17</v>
       </c>
       <c r="K149" t="n">
-        <v>1.755441115818343</v>
+        <v>1.757496593321768</v>
       </c>
       <c r="L149" t="n">
         <v>23.00640339859842</v>
       </c>
       <c r="M149" t="n">
-        <v>2.249804039781183</v>
+        <v>35.18710400624892</v>
       </c>
       <c r="N149" t="n">
-        <v>1.141062351849522</v>
+        <v>0.8844864169514772</v>
       </c>
       <c r="O149" t="n">
-        <v>1.695433195815352</v>
+        <v>18.0357952116002</v>
       </c>
       <c r="P149" t="b">
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>-3.539385695119202</v>
+        <v>90.25550815640561</v>
       </c>
     </row>
     <row r="150">
@@ -9111,25 +8943,25 @@
         <v>17</v>
       </c>
       <c r="K150" t="n">
-        <v>1.755441115818343</v>
+        <v>1.757496593321768</v>
       </c>
       <c r="L150" t="n">
         <v>23.01601892099487</v>
       </c>
       <c r="M150" t="n">
-        <v>2.249804039781183</v>
+        <v>35.18710400624892</v>
       </c>
       <c r="N150" t="n">
-        <v>1.141062351849522</v>
+        <v>0.8844864169514772</v>
       </c>
       <c r="O150" t="n">
-        <v>1.695433195815352</v>
+        <v>18.0357952116002</v>
       </c>
       <c r="P150" t="b">
         <v>1</v>
       </c>
       <c r="Q150" t="n">
-        <v>-3.539385695119202</v>
+        <v>90.25550815640561</v>
       </c>
     </row>
     <row r="151">
@@ -9170,25 +9002,25 @@
         <v>17</v>
       </c>
       <c r="K151" t="n">
-        <v>1.788673379144996</v>
+        <v>1.789005990939995</v>
       </c>
       <c r="L151" t="n">
         <v>23.11631786878887</v>
       </c>
       <c r="M151" t="n">
-        <v>2.276935456485526</v>
+        <v>35.1831624682064</v>
       </c>
       <c r="N151" t="n">
-        <v>1.141062351849522</v>
+        <v>0.8844864169514772</v>
       </c>
       <c r="O151" t="n">
-        <v>1.708998904167524</v>
+        <v>18.03382444257894</v>
       </c>
       <c r="P151" t="b">
         <v>1</v>
       </c>
       <c r="Q151" t="n">
-        <v>-4.662055357857753</v>
+        <v>90.07971938156365</v>
       </c>
     </row>
     <row r="152">
@@ -9229,25 +9061,25 @@
         <v>17</v>
       </c>
       <c r="K152" t="n">
-        <v>1.778274352829337</v>
+        <v>1.778211637127946</v>
       </c>
       <c r="L152" t="n">
         <v>23.32435668514661</v>
       </c>
       <c r="M152" t="n">
-        <v>2.313323918834337</v>
+        <v>32.25135624930163</v>
       </c>
       <c r="N152" t="n">
-        <v>1.191043762367248</v>
+        <v>0.8418695730956948</v>
       </c>
       <c r="O152" t="n">
-        <v>1.752183840600793</v>
+        <v>16.54661291119866</v>
       </c>
       <c r="P152" t="b">
         <v>1</v>
       </c>
       <c r="Q152" t="n">
-        <v>-1.48902824144288</v>
+        <v>89.25331941545292</v>
       </c>
     </row>
     <row r="153">
@@ -9288,25 +9120,25 @@
         <v>17</v>
       </c>
       <c r="K153" t="n">
-        <v>1.778274352829337</v>
+        <v>1.778211637127946</v>
       </c>
       <c r="L153" t="n">
         <v>23.35274664225318</v>
       </c>
       <c r="M153" t="n">
-        <v>2.313323918834337</v>
+        <v>32.25135624930163</v>
       </c>
       <c r="N153" t="n">
-        <v>1.191043762367248</v>
+        <v>0.8418695730956948</v>
       </c>
       <c r="O153" t="n">
-        <v>1.752183840600793</v>
+        <v>16.54661291119866</v>
       </c>
       <c r="P153" t="b">
         <v>1</v>
       </c>
       <c r="Q153" t="n">
-        <v>-1.48902824144288</v>
+        <v>89.25331941545292</v>
       </c>
     </row>
     <row r="154">
@@ -9347,25 +9179,25 @@
         <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>1.772817011596296</v>
+        <v>1.77206441721475</v>
       </c>
       <c r="L154" t="n">
         <v>23.51647814236181</v>
       </c>
       <c r="M154" t="n">
-        <v>2.282193623509603</v>
+        <v>3.642125819453386</v>
       </c>
       <c r="N154" t="n">
-        <v>1.486028554703088</v>
+        <v>0.6930677684189502</v>
       </c>
       <c r="O154" t="n">
-        <v>1.884111089106346</v>
+        <v>2.167596793936168</v>
       </c>
       <c r="P154" t="b">
         <v>1</v>
       </c>
       <c r="Q154" t="n">
-        <v>5.906980652761728</v>
+        <v>18.2475070007446</v>
       </c>
     </row>
     <row r="155">
@@ -9406,25 +9238,25 @@
         <v>17</v>
       </c>
       <c r="K155" t="n">
-        <v>1.752865128020558</v>
+        <v>1.751891028671269</v>
       </c>
       <c r="L155" t="n">
         <v>23.67665503477312</v>
       </c>
       <c r="M155" t="n">
-        <v>2.261802382317713</v>
+        <v>3.255358354232785</v>
       </c>
       <c r="N155" t="n">
-        <v>1.547807787268301</v>
+        <v>0.6930677684189502</v>
       </c>
       <c r="O155" t="n">
-        <v>1.904805084793007</v>
+        <v>1.974213061325868</v>
       </c>
       <c r="P155" t="b">
         <v>1</v>
       </c>
       <c r="Q155" t="n">
-        <v>7.976666903372964</v>
+        <v>11.2612988440715</v>
       </c>
     </row>
     <row r="156">
@@ -9465,25 +9297,25 @@
         <v>17</v>
       </c>
       <c r="K156" t="n">
-        <v>1.701855296213878</v>
+        <v>1.69915042491716</v>
       </c>
       <c r="L156" t="n">
         <v>23.72993427332839</v>
       </c>
       <c r="M156" t="n">
-        <v>2.261802382317713</v>
+        <v>3.255358354232785</v>
       </c>
       <c r="N156" t="n">
-        <v>1.547807787268301</v>
+        <v>0.6930677684189502</v>
       </c>
       <c r="O156" t="n">
-        <v>1.904805084793007</v>
+        <v>1.974213061325868</v>
       </c>
       <c r="P156" t="b">
         <v>1</v>
       </c>
       <c r="Q156" t="n">
-        <v>10.65462236526861</v>
+        <v>13.932773609753</v>
       </c>
     </row>
     <row r="157">
@@ -9524,25 +9356,25 @@
         <v>17</v>
       </c>
       <c r="K157" t="n">
-        <v>1.39792805562581</v>
+        <v>1.395470510692885</v>
       </c>
       <c r="L157" t="n">
         <v>24.1090519659607</v>
       </c>
       <c r="M157" t="n">
-        <v>2.29998581674779</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="N157" t="n">
-        <v>1.841571538570617</v>
+        <v>0.5461080070969886</v>
       </c>
       <c r="O157" t="n">
-        <v>2.070778677659204</v>
+        <v>1.472107001699288</v>
       </c>
       <c r="P157" t="b">
         <v>1</v>
       </c>
       <c r="Q157" t="n">
-        <v>32.49263812171274</v>
+        <v>5.205904932042271</v>
       </c>
     </row>
     <row r="158">
@@ -9583,25 +9415,25 @@
         <v>17</v>
       </c>
       <c r="K158" t="n">
-        <v>1.39792805562581</v>
+        <v>1.395470510692885</v>
       </c>
       <c r="L158" t="n">
         <v>24.16752380890742</v>
       </c>
       <c r="M158" t="n">
-        <v>2.29998581674779</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="N158" t="n">
-        <v>1.841571538570617</v>
+        <v>0.5461080070969886</v>
       </c>
       <c r="O158" t="n">
-        <v>2.070778677659204</v>
+        <v>1.472107001699288</v>
       </c>
       <c r="P158" t="b">
         <v>1</v>
       </c>
       <c r="Q158" t="n">
-        <v>32.49263812171274</v>
+        <v>5.205904932042271</v>
       </c>
     </row>
     <row r="159">
@@ -9642,25 +9474,25 @@
         <v>17</v>
       </c>
       <c r="K159" t="n">
-        <v>1.327320467937538</v>
+        <v>1.324849022762463</v>
       </c>
       <c r="L159" t="n">
         <v>24.22405432136471</v>
       </c>
       <c r="M159" t="n">
-        <v>2.29998581674779</v>
+        <v>2.398105996301588</v>
       </c>
       <c r="N159" t="n">
-        <v>1.841571538570617</v>
+        <v>0.5461080070969886</v>
       </c>
       <c r="O159" t="n">
-        <v>2.070778677659204</v>
+        <v>1.472107001699288</v>
       </c>
       <c r="P159" t="b">
         <v>1</v>
       </c>
       <c r="Q159" t="n">
-        <v>35.90235005520079</v>
+        <v>10.00321163929261</v>
       </c>
     </row>
     <row r="160">
@@ -9701,25 +9533,25 @@
         <v>17</v>
       </c>
       <c r="K160" t="n">
-        <v>1.1971891976014</v>
+        <v>1.195349386467163</v>
       </c>
       <c r="L160" t="n">
         <v>24.41037621139587</v>
       </c>
       <c r="M160" t="n">
-        <v>2.39899655611404</v>
+        <v>2.354719534730244</v>
       </c>
       <c r="N160" t="n">
-        <v>1.643774409243683</v>
+        <v>0.5391736064784913</v>
       </c>
       <c r="O160" t="n">
-        <v>2.021385482678862</v>
+        <v>1.446946570604368</v>
       </c>
       <c r="P160" t="b">
         <v>1</v>
       </c>
       <c r="Q160" t="n">
-        <v>40.77383023376557</v>
+        <v>17.38814613120898</v>
       </c>
     </row>
     <row r="161">
@@ -9760,25 +9592,25 @@
         <v>17</v>
       </c>
       <c r="K161" t="n">
-        <v>1.1971891976014</v>
+        <v>1.195349386467163</v>
       </c>
       <c r="L161" t="n">
         <v>24.41188090518083</v>
       </c>
       <c r="M161" t="n">
-        <v>2.39899655611404</v>
+        <v>2.354719534730244</v>
       </c>
       <c r="N161" t="n">
-        <v>1.643774409243683</v>
+        <v>0.5391736064784913</v>
       </c>
       <c r="O161" t="n">
-        <v>2.021385482678862</v>
+        <v>1.446946570604368</v>
       </c>
       <c r="P161" t="b">
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>40.77383023376557</v>
+        <v>17.38814613120898</v>
       </c>
     </row>
     <row r="162">
@@ -9819,25 +9651,25 @@
         <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>1.1971891976014</v>
+        <v>1.195349386467163</v>
       </c>
       <c r="L162" t="n">
         <v>24.4791278709022</v>
       </c>
       <c r="M162" t="n">
-        <v>2.426003596047259</v>
+        <v>2.354719534730244</v>
       </c>
       <c r="N162" t="n">
-        <v>1.555805184715616</v>
+        <v>0.5391736064784913</v>
       </c>
       <c r="O162" t="n">
-        <v>1.990904390381438</v>
+        <v>1.446946570604368</v>
       </c>
       <c r="P162" t="b">
         <v>1</v>
       </c>
       <c r="Q162" t="n">
-        <v>39.86706727930663</v>
+        <v>17.38814613120898</v>
       </c>
     </row>
     <row r="163">
@@ -9878,25 +9710,25 @@
         <v>17</v>
       </c>
       <c r="K163" t="n">
-        <v>1.144755081883404</v>
+        <v>1.143138415192682</v>
       </c>
       <c r="L163" t="n">
         <v>24.51465005327394</v>
       </c>
       <c r="M163" t="n">
-        <v>2.426003596047259</v>
+        <v>2.354719534730244</v>
       </c>
       <c r="N163" t="n">
-        <v>1.555805184715616</v>
+        <v>0.5528163966377017</v>
       </c>
       <c r="O163" t="n">
-        <v>1.990904390381438</v>
+        <v>1.453767965683973</v>
       </c>
       <c r="P163" t="b">
         <v>1</v>
       </c>
       <c r="Q163" t="n">
-        <v>42.50075054261746</v>
+        <v>21.36720287031124</v>
       </c>
     </row>
     <row r="164">
@@ -9937,25 +9769,25 @@
         <v>17</v>
       </c>
       <c r="K164" t="n">
-        <v>1.110326020176739</v>
+        <v>1.109699562533763</v>
       </c>
       <c r="L164" t="n">
         <v>24.69721341287469</v>
       </c>
       <c r="M164" t="n">
-        <v>2.43304178777875</v>
+        <v>2.251765918996991</v>
       </c>
       <c r="N164" t="n">
-        <v>1.278466120075154</v>
+        <v>0.5528163966377017</v>
       </c>
       <c r="O164" t="n">
-        <v>1.855753953926952</v>
+        <v>1.402291157817346</v>
       </c>
       <c r="P164" t="b">
         <v>1</v>
       </c>
       <c r="Q164" t="n">
-        <v>40.16846803278079</v>
+        <v>20.86525281518569</v>
       </c>
     </row>
     <row r="165">
@@ -9996,25 +9828,25 @@
         <v>17</v>
       </c>
       <c r="K165" t="n">
-        <v>1.127592304758405</v>
+        <v>1.127925107555623</v>
       </c>
       <c r="L165" t="n">
         <v>24.88677464644601</v>
       </c>
       <c r="M165" t="n">
-        <v>2.329533845651123</v>
+        <v>2.218923888940998</v>
       </c>
       <c r="N165" t="n">
-        <v>1.200149342274758</v>
+        <v>0.6869367356473498</v>
       </c>
       <c r="O165" t="n">
-        <v>1.76484159396294</v>
+        <v>1.452930312294174</v>
       </c>
       <c r="P165" t="b">
         <v>1</v>
       </c>
       <c r="Q165" t="n">
-        <v>36.10801623128089</v>
+        <v>22.36894653435707</v>
       </c>
     </row>
     <row r="166">
@@ -10055,25 +9887,25 @@
         <v>17</v>
       </c>
       <c r="K166" t="n">
-        <v>1.129235734728124</v>
+        <v>1.128999637704991</v>
       </c>
       <c r="L166" t="n">
         <v>24.92314013126968</v>
       </c>
       <c r="M166" t="n">
-        <v>2.329533845651123</v>
+        <v>2.218923888940998</v>
       </c>
       <c r="N166" t="n">
-        <v>1.200149342274758</v>
+        <v>0.7109010806737983</v>
       </c>
       <c r="O166" t="n">
-        <v>1.76484159396294</v>
+        <v>1.464912484807398</v>
       </c>
       <c r="P166" t="b">
         <v>1</v>
       </c>
       <c r="Q166" t="n">
-        <v>36.01489569426835</v>
+        <v>22.93057439172358</v>
       </c>
     </row>
     <row r="167">
@@ -10114,25 +9946,25 @@
         <v>17</v>
       </c>
       <c r="K167" t="n">
-        <v>1.129235734728124</v>
+        <v>1.128999637704991</v>
       </c>
       <c r="L167" t="n">
         <v>24.9316115630532</v>
       </c>
       <c r="M167" t="n">
-        <v>2.329533845651123</v>
+        <v>2.218923888940998</v>
       </c>
       <c r="N167" t="n">
-        <v>1.200149342274758</v>
+        <v>0.7109010806737983</v>
       </c>
       <c r="O167" t="n">
-        <v>1.76484159396294</v>
+        <v>1.464912484807398</v>
       </c>
       <c r="P167" t="b">
         <v>1</v>
       </c>
       <c r="Q167" t="n">
-        <v>36.01489569426835</v>
+        <v>22.93057439172358</v>
       </c>
     </row>
     <row r="168">
@@ -10173,25 +10005,25 @@
         <v>17</v>
       </c>
       <c r="K168" t="n">
-        <v>1.129235734728124</v>
+        <v>1.128999637704991</v>
       </c>
       <c r="L168" t="n">
         <v>24.95603322515469</v>
       </c>
       <c r="M168" t="n">
-        <v>2.329533845651123</v>
+        <v>2.218923888940998</v>
       </c>
       <c r="N168" t="n">
-        <v>1.200149342274758</v>
+        <v>0.7109010806737983</v>
       </c>
       <c r="O168" t="n">
-        <v>1.76484159396294</v>
+        <v>1.464912484807398</v>
       </c>
       <c r="P168" t="b">
         <v>1</v>
       </c>
       <c r="Q168" t="n">
-        <v>36.01489569426835</v>
+        <v>22.93057439172358</v>
       </c>
     </row>
     <row r="169">
@@ -10232,25 +10064,25 @@
         <v>17</v>
       </c>
       <c r="K169" t="n">
-        <v>1.07931209195279</v>
+        <v>1.078132302319271</v>
       </c>
       <c r="L169" t="n">
         <v>25.20044253403735</v>
       </c>
       <c r="M169" t="n">
-        <v>2.129964220088542</v>
+        <v>2.253347188363659</v>
       </c>
       <c r="N169" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="O169" t="n">
-        <v>1.497929025642587</v>
+        <v>1.444190323302428</v>
       </c>
       <c r="P169" t="b">
         <v>1</v>
       </c>
       <c r="Q169" t="n">
-        <v>27.9463797365311</v>
+        <v>25.34693766304245</v>
       </c>
     </row>
     <row r="170">
@@ -10291,25 +10123,25 @@
         <v>17</v>
       </c>
       <c r="K170" t="n">
-        <v>1.007523819185527</v>
+        <v>1.006580384496336</v>
       </c>
       <c r="L170" t="n">
         <v>25.39719265788</v>
       </c>
       <c r="M170" t="n">
-        <v>1.726676601806959</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="N170" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="O170" t="n">
-        <v>1.296285216501796</v>
+        <v>1.468129980450201</v>
       </c>
       <c r="P170" t="b">
         <v>1</v>
       </c>
       <c r="Q170" t="n">
-        <v>22.27606962112327</v>
+        <v>31.4379245775181</v>
       </c>
     </row>
     <row r="171">
@@ -10350,25 +10182,25 @@
         <v>17</v>
       </c>
       <c r="K171" t="n">
-        <v>0.9898694112683336</v>
+        <v>0.9899388197681704</v>
       </c>
       <c r="L171" t="n">
         <v>25.48650433058561</v>
       </c>
       <c r="M171" t="n">
-        <v>1.726676601806959</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="N171" t="n">
-        <v>0.7954039355764896</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="O171" t="n">
-        <v>1.261040268691724</v>
+        <v>1.468129980450201</v>
       </c>
       <c r="P171" t="b">
         <v>1</v>
       </c>
       <c r="Q171" t="n">
-        <v>21.50374291415125</v>
+        <v>32.57144578815792</v>
       </c>
     </row>
     <row r="172">
@@ -10409,25 +10241,25 @@
         <v>17</v>
       </c>
       <c r="K172" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.9914318695966965</v>
       </c>
       <c r="L172" t="n">
         <v>25.53264810457242</v>
       </c>
       <c r="M172" t="n">
-        <v>1.726676601806959</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="N172" t="n">
-        <v>0.7954039355764896</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="O172" t="n">
-        <v>1.261040268691724</v>
+        <v>1.468129980450201</v>
       </c>
       <c r="P172" t="b">
         <v>1</v>
       </c>
       <c r="Q172" t="n">
-        <v>21.37806144768908</v>
+        <v>32.469748401114</v>
       </c>
     </row>
     <row r="173">
@@ -10468,25 +10300,25 @@
         <v>17</v>
       </c>
       <c r="K173" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.9914318695966965</v>
       </c>
       <c r="L173" t="n">
         <v>25.54471823351573</v>
       </c>
       <c r="M173" t="n">
-        <v>1.726676601806959</v>
+        <v>2.301226502659204</v>
       </c>
       <c r="N173" t="n">
-        <v>0.7954039355764896</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="O173" t="n">
-        <v>1.261040268691724</v>
+        <v>1.468129980450201</v>
       </c>
       <c r="P173" t="b">
         <v>1</v>
       </c>
       <c r="Q173" t="n">
-        <v>21.37806144768908</v>
+        <v>32.469748401114</v>
       </c>
     </row>
     <row r="174">
@@ -10527,25 +10359,25 @@
         <v>17</v>
       </c>
       <c r="K174" t="n">
-        <v>1.06923049452409</v>
+        <v>1.070830314670122</v>
       </c>
       <c r="L174" t="n">
         <v>25.97566595125633</v>
       </c>
       <c r="M174" t="n">
-        <v>1.140911278710099</v>
+        <v>2.655054926060676</v>
       </c>
       <c r="N174" t="n">
-        <v>0.5385163421711662</v>
+        <v>0.5295971516601461</v>
       </c>
       <c r="O174" t="n">
-        <v>0.8397138104406328</v>
+        <v>1.592326038860411</v>
       </c>
       <c r="P174" t="b">
         <v>1</v>
       </c>
       <c r="Q174" t="n">
-        <v>-27.33272708269738</v>
+        <v>32.75056184872233</v>
       </c>
     </row>
     <row r="175">
@@ -10586,25 +10418,25 @@
         <v>17</v>
       </c>
       <c r="K175" t="n">
-        <v>1.187175472566269</v>
+        <v>1.189002425173676</v>
       </c>
       <c r="L175" t="n">
         <v>26.18154688434244</v>
       </c>
       <c r="M175" t="n">
-        <v>1.140911278710099</v>
+        <v>2.643513293066809</v>
       </c>
       <c r="N175" t="n">
-        <v>0.4522874703617749</v>
+        <v>0.5371396317144246</v>
       </c>
       <c r="O175" t="n">
-        <v>0.7965993745359372</v>
+        <v>1.590326462390617</v>
       </c>
       <c r="P175" t="b">
         <v>1</v>
       </c>
       <c r="Q175" t="n">
-        <v>-49.03042991439255</v>
+        <v>25.23532411160793</v>
       </c>
     </row>
     <row r="176">
@@ -10645,25 +10477,25 @@
         <v>17</v>
       </c>
       <c r="K176" t="n">
-        <v>1.333556077280552</v>
+        <v>1.333565658438912</v>
       </c>
       <c r="L176" t="n">
         <v>26.43512143056763</v>
       </c>
       <c r="M176" t="n">
-        <v>0.947668382193923</v>
+        <v>2.518260643654614</v>
       </c>
       <c r="N176" t="n">
-        <v>0.4041573121506322</v>
+        <v>0.4466851048168524</v>
       </c>
       <c r="O176" t="n">
-        <v>0.6759128471722776</v>
+        <v>1.482472874235733</v>
       </c>
       <c r="P176" t="b">
         <v>1</v>
       </c>
       <c r="Q176" t="n">
-        <v>-97.29704544891624</v>
+        <v>10.04451537594493</v>
       </c>
     </row>
     <row r="177">
@@ -10704,25 +10536,25 @@
         <v>17</v>
       </c>
       <c r="K177" t="n">
-        <v>1.312922373703677</v>
+        <v>1.311819253749365</v>
       </c>
       <c r="L177" t="n">
         <v>26.59877290502622</v>
       </c>
       <c r="M177" t="n">
-        <v>0.947668382193923</v>
+        <v>2.340871106880618</v>
       </c>
       <c r="N177" t="n">
-        <v>0.4213399913646258</v>
+        <v>0.4466851048168524</v>
       </c>
       <c r="O177" t="n">
-        <v>0.6845041867792744</v>
+        <v>1.393778105848735</v>
       </c>
       <c r="P177" t="b">
         <v>1</v>
       </c>
       <c r="Q177" t="n">
-        <v>-91.80633209582444</v>
+        <v>5.880337175296746</v>
       </c>
     </row>
     <row r="178">
@@ -10763,25 +10595,25 @@
         <v>17</v>
       </c>
       <c r="K178" t="n">
-        <v>1.269293198848958</v>
+        <v>1.26813063008406</v>
       </c>
       <c r="L178" t="n">
         <v>26.64036311602185</v>
       </c>
       <c r="M178" t="n">
-        <v>0.947668382193923</v>
+        <v>2.340871106880618</v>
       </c>
       <c r="N178" t="n">
-        <v>0.4213399913646258</v>
+        <v>0.4466851048168524</v>
       </c>
       <c r="O178" t="n">
-        <v>0.6845041867792744</v>
+        <v>1.393778105848735</v>
       </c>
       <c r="P178" t="b">
         <v>1</v>
       </c>
       <c r="Q178" t="n">
-        <v>-85.43249601163578</v>
+        <v>9.014883734894241</v>
       </c>
     </row>
     <row r="179">
@@ -10822,25 +10654,25 @@
         <v>17</v>
       </c>
       <c r="K179" t="n">
-        <v>1.269293198848958</v>
+        <v>1.26813063008406</v>
       </c>
       <c r="L179" t="n">
         <v>26.66118302218647</v>
       </c>
       <c r="M179" t="n">
-        <v>0.947668382193923</v>
+        <v>2.340871106880618</v>
       </c>
       <c r="N179" t="n">
-        <v>0.4213399913646258</v>
+        <v>0.4466851048168524</v>
       </c>
       <c r="O179" t="n">
-        <v>0.6845041867792744</v>
+        <v>1.393778105848735</v>
       </c>
       <c r="P179" t="b">
         <v>1</v>
       </c>
       <c r="Q179" t="n">
-        <v>-85.43249601163578</v>
+        <v>9.014883734894241</v>
       </c>
     </row>
     <row r="180">
@@ -10881,25 +10713,25 @@
         <v>17</v>
       </c>
       <c r="K180" t="n">
-        <v>1.167607646918589</v>
+        <v>1.167201635602541</v>
       </c>
       <c r="L180" t="n">
         <v>27.01340579349124</v>
       </c>
       <c r="M180" t="n">
-        <v>1.094491209829949</v>
+        <v>2.216829882042773</v>
       </c>
       <c r="N180" t="n">
-        <v>0.470025857502466</v>
+        <v>0.2749575999425046</v>
       </c>
       <c r="O180" t="n">
-        <v>0.7822585336662076</v>
+        <v>1.245893740992639</v>
       </c>
       <c r="P180" t="b">
         <v>1</v>
       </c>
       <c r="Q180" t="n">
-        <v>-49.26109421221236</v>
+        <v>6.316116920805904</v>
       </c>
     </row>
     <row r="181">
@@ -10940,25 +10772,25 @@
         <v>17</v>
       </c>
       <c r="K181" t="n">
-        <v>1.058335978988722</v>
+        <v>1.057776064385731</v>
       </c>
       <c r="L181" t="n">
         <v>27.306515075519</v>
       </c>
       <c r="M181" t="n">
-        <v>1.160223779553904</v>
+        <v>2.184586328633258</v>
       </c>
       <c r="N181" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.1619014299351722</v>
       </c>
       <c r="O181" t="n">
-        <v>0.9390889527536648</v>
+        <v>1.173243879284215</v>
       </c>
       <c r="P181" t="b">
         <v>1</v>
       </c>
       <c r="Q181" t="n">
-        <v>-12.69816090215865</v>
+        <v>9.841757279733676</v>
       </c>
     </row>
     <row r="182">
@@ -10999,25 +10831,25 @@
         <v>17</v>
       </c>
       <c r="K182" t="n">
-        <v>1.072186129913543</v>
+        <v>1.072418604357054</v>
       </c>
       <c r="L182" t="n">
         <v>27.48176118377377</v>
       </c>
       <c r="M182" t="n">
-        <v>1.427812544501824</v>
+        <v>2.122383846363779</v>
       </c>
       <c r="N182" t="n">
-        <v>0.8504789130187842</v>
+        <v>0.1229522451865707</v>
       </c>
       <c r="O182" t="n">
-        <v>1.139145728760304</v>
+        <v>1.122668045775175</v>
       </c>
       <c r="P182" t="b">
         <v>1</v>
       </c>
       <c r="Q182" t="n">
-        <v>5.878053804374217</v>
+        <v>4.475894865558871</v>
       </c>
     </row>
     <row r="183">
@@ -11058,25 +10890,25 @@
         <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>1.104115376478233</v>
+        <v>1.104810542344077</v>
       </c>
       <c r="L183" t="n">
         <v>27.80773239529702</v>
       </c>
       <c r="M183" t="n">
-        <v>1.427812544501824</v>
+        <v>2.251000276695078</v>
       </c>
       <c r="N183" t="n">
-        <v>0.9315183779958096</v>
+        <v>0.09074520326948515</v>
       </c>
       <c r="O183" t="n">
-        <v>1.179665461248817</v>
+        <v>1.170872739982282</v>
       </c>
       <c r="P183" t="b">
         <v>1</v>
       </c>
       <c r="Q183" t="n">
-        <v>6.404365241871646</v>
+        <v>5.642133033108676</v>
       </c>
     </row>
     <row r="184">
@@ -11117,26 +10949,20 @@
         <v>17</v>
       </c>
       <c r="K184" t="n">
-        <v>1.141062351849522</v>
+        <v>1.141152858016309</v>
       </c>
       <c r="L184" t="n">
         <v>28.0254682295774</v>
       </c>
       <c r="M184" t="n">
-        <v>1.755441115818343</v>
-      </c>
-      <c r="N184" t="n">
-        <v>0.8851152668858296</v>
-      </c>
-      <c r="O184" t="n">
-        <v>1.320278191352086</v>
-      </c>
+        <v>2.251000276695078</v>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
       <c r="P184" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>13.57409678327195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -11176,26 +11002,20 @@
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>1.191043762367248</v>
+        <v>1.192255315039814</v>
       </c>
       <c r="L185" t="n">
         <v>28.22962768949274</v>
       </c>
       <c r="M185" t="n">
-        <v>1.778274352829337</v>
-      </c>
-      <c r="N185" t="n">
-        <v>0.8426817177160192</v>
-      </c>
-      <c r="O185" t="n">
-        <v>1.310478035272678</v>
-      </c>
+        <v>2.313867334222721</v>
+      </c>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
       <c r="P185" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>9.113794332354374</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -11235,26 +11055,20 @@
         <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>1.191043762367248</v>
+        <v>1.192255315039814</v>
       </c>
       <c r="L186" t="n">
         <v>28.23293910160864</v>
       </c>
       <c r="M186" t="n">
-        <v>1.778274352829337</v>
-      </c>
-      <c r="N186" t="n">
-        <v>0.8426817177160192</v>
-      </c>
-      <c r="O186" t="n">
-        <v>1.310478035272678</v>
-      </c>
+        <v>2.313867334222721</v>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
       <c r="P186" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>9.113794332354374</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -11294,26 +11108,20 @@
         <v>17</v>
       </c>
       <c r="K187" t="n">
-        <v>1.486028554703088</v>
+        <v>1.487461797283134</v>
       </c>
       <c r="L187" t="n">
         <v>28.54426913963886</v>
       </c>
       <c r="M187" t="n">
-        <v>1.772817011596296</v>
-      </c>
-      <c r="N187" t="n">
-        <v>0.6938713116664846</v>
-      </c>
-      <c r="O187" t="n">
-        <v>1.23334416163139</v>
-      </c>
+        <v>2.281309496953031</v>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
       <c r="P187" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>-20.48774388630203</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11353,26 +11161,20 @@
         <v>17</v>
       </c>
       <c r="K188" t="n">
-        <v>1.547807787268301</v>
+        <v>1.548748605141129</v>
       </c>
       <c r="L188" t="n">
         <v>28.60555803709645</v>
       </c>
       <c r="M188" t="n">
-        <v>1.752865128020558</v>
-      </c>
-      <c r="N188" t="n">
-        <v>0.6938713116664846</v>
-      </c>
-      <c r="O188" t="n">
-        <v>1.223368219843521</v>
-      </c>
+        <v>2.281309496953031</v>
+      </c>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
       <c r="P188" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>-26.52018927435258</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11412,26 +11214,20 @@
         <v>17</v>
       </c>
       <c r="K189" t="n">
-        <v>1.844475967958824</v>
+        <v>1.844802313212991</v>
       </c>
       <c r="L189" t="n">
         <v>28.9730213849947</v>
       </c>
       <c r="M189" t="n">
-        <v>1.39792805562581</v>
-      </c>
-      <c r="N189" t="n">
-        <v>0.5629841550136426</v>
-      </c>
-      <c r="O189" t="n">
-        <v>0.9804561053197263</v>
-      </c>
+        <v>2.278718840385056</v>
+      </c>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
       <c r="P189" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>-88.12427786936384</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11471,26 +11267,20 @@
         <v>17</v>
       </c>
       <c r="K190" t="n">
-        <v>1.841571538570617</v>
+        <v>1.84114621481359</v>
       </c>
       <c r="L190" t="n">
         <v>29.10940974915959</v>
       </c>
       <c r="M190" t="n">
-        <v>1.39792805562581</v>
-      </c>
-      <c r="N190" t="n">
-        <v>0.5463302263033294</v>
-      </c>
-      <c r="O190" t="n">
-        <v>0.9721291409645697</v>
-      </c>
+        <v>2.300988819494015</v>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
       <c r="P190" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>-89.43692365227997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11530,26 +11320,20 @@
         <v>17</v>
       </c>
       <c r="K191" t="n">
-        <v>1.841571538570617</v>
+        <v>1.84114621481359</v>
       </c>
       <c r="L191" t="n">
         <v>29.16126322305756</v>
       </c>
       <c r="M191" t="n">
-        <v>1.39792805562581</v>
-      </c>
-      <c r="N191" t="n">
-        <v>0.5463302263033294</v>
-      </c>
-      <c r="O191" t="n">
-        <v>0.9721291409645697</v>
-      </c>
+        <v>2.300988819494015</v>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
       <c r="P191" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>-89.43692365227997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11589,26 +11373,20 @@
         <v>17</v>
       </c>
       <c r="K192" t="n">
-        <v>1.720576971928573</v>
+        <v>1.719355082918982</v>
       </c>
       <c r="L192" t="n">
         <v>29.316584569303</v>
       </c>
       <c r="M192" t="n">
-        <v>1.327320467937538</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0.5389585101632535</v>
-      </c>
-      <c r="O192" t="n">
-        <v>0.9331394890503959</v>
-      </c>
+        <v>2.400491992516112</v>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>-84.38582785511606</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11648,26 +11426,20 @@
         <v>17</v>
       </c>
       <c r="K193" t="n">
-        <v>1.643774409243683</v>
+        <v>1.642536369273613</v>
       </c>
       <c r="L193" t="n">
         <v>29.40702891094307</v>
       </c>
       <c r="M193" t="n">
-        <v>1.1971891976014</v>
-      </c>
-      <c r="N193" t="n">
-        <v>0.5389585101632535</v>
-      </c>
-      <c r="O193" t="n">
-        <v>0.8680738538823268</v>
-      </c>
+        <v>2.400491992516112</v>
+      </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
       <c r="P193" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>-89.35882032296621</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11707,26 +11479,20 @@
         <v>17</v>
       </c>
       <c r="K194" t="n">
-        <v>1.643774409243683</v>
+        <v>1.642536369273613</v>
       </c>
       <c r="L194" t="n">
         <v>29.45539047480333</v>
       </c>
       <c r="M194" t="n">
-        <v>1.1971891976014</v>
-      </c>
-      <c r="N194" t="n">
-        <v>0.5389585101632535</v>
-      </c>
-      <c r="O194" t="n">
-        <v>0.8680738538823268</v>
-      </c>
+        <v>2.426433234651199</v>
+      </c>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>-89.35882032296621</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11766,26 +11532,20 @@
         <v>17</v>
       </c>
       <c r="K195" t="n">
-        <v>1.555805184715616</v>
+        <v>1.554274485292735</v>
       </c>
       <c r="L195" t="n">
         <v>29.48543700265353</v>
       </c>
       <c r="M195" t="n">
-        <v>1.1971891976014</v>
-      </c>
-      <c r="N195" t="n">
-        <v>0.5389585101632535</v>
-      </c>
-      <c r="O195" t="n">
-        <v>0.8680738538823268</v>
-      </c>
+        <v>2.426433234651199</v>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
       <c r="P195" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>-79.22497927538275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11825,26 +11585,20 @@
         <v>17</v>
       </c>
       <c r="K196" t="n">
-        <v>1.278466120075154</v>
+        <v>1.277410331539602</v>
       </c>
       <c r="L196" t="n">
         <v>29.82306783792539</v>
       </c>
       <c r="M196" t="n">
-        <v>1.127592304758405</v>
-      </c>
-      <c r="N196" t="n">
-        <v>0.6865475192796013</v>
-      </c>
-      <c r="O196" t="n">
-        <v>0.9070699120190033</v>
-      </c>
+        <v>2.328854369026954</v>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
       <c r="P196" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>-40.94460670947373</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11884,26 +11638,20 @@
         <v>17</v>
       </c>
       <c r="K197" t="n">
-        <v>1.200149342274758</v>
+        <v>1.19907899481458</v>
       </c>
       <c r="L197" t="n">
         <v>29.93102075891164</v>
       </c>
       <c r="M197" t="n">
-        <v>1.129235734728124</v>
-      </c>
-      <c r="N197" t="n">
-        <v>0.7107101364517812</v>
-      </c>
-      <c r="O197" t="n">
-        <v>0.9199729355899527</v>
-      </c>
+        <v>2.328854369026954</v>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
       <c r="P197" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>-30.45485316425491</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11943,26 +11691,20 @@
         <v>17</v>
       </c>
       <c r="K198" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.8651156562453568</v>
       </c>
       <c r="L198" t="n">
         <v>30.31357008875478</v>
       </c>
       <c r="M198" t="n">
-        <v>1.007523819185527</v>
-      </c>
-      <c r="N198" t="n">
-        <v>0.6353390966846304</v>
-      </c>
-      <c r="O198" t="n">
-        <v>0.8214314579350789</v>
-      </c>
+        <v>2.128291034343583</v>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
       <c r="P198" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>-5.412791637335657</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -12002,26 +11744,20 @@
         <v>17</v>
       </c>
       <c r="K199" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.8651156562453568</v>
       </c>
       <c r="L199" t="n">
         <v>30.32819470675391</v>
       </c>
       <c r="M199" t="n">
-        <v>1.007523819185527</v>
-      </c>
-      <c r="N199" t="n">
-        <v>0.6353390966846304</v>
-      </c>
-      <c r="O199" t="n">
-        <v>0.8214314579350789</v>
-      </c>
+        <v>2.128291034343583</v>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
       <c r="P199" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>-5.412791637335657</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -12061,26 +11797,20 @@
         <v>17</v>
       </c>
       <c r="K200" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.8651156562453568</v>
       </c>
       <c r="L200" t="n">
         <v>30.36857385734933</v>
       </c>
       <c r="M200" t="n">
-        <v>1.007523819185527</v>
-      </c>
-      <c r="N200" t="n">
-        <v>0.6353390966846304</v>
-      </c>
-      <c r="O200" t="n">
-        <v>0.8214314579350789</v>
-      </c>
+        <v>2.128291034343583</v>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
       <c r="P200" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>-5.412791637335657</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -12120,26 +11850,20 @@
         <v>17</v>
       </c>
       <c r="K201" t="n">
-        <v>0.7954039355764896</v>
+        <v>0.7945090211968119</v>
       </c>
       <c r="L201" t="n">
         <v>30.4723715647018</v>
       </c>
       <c r="M201" t="n">
-        <v>0.9898694112683336</v>
-      </c>
-      <c r="N201" t="n">
-        <v>0.6353390966846304</v>
-      </c>
-      <c r="O201" t="n">
-        <v>0.8126042539764819</v>
-      </c>
+        <v>1.720801904835842</v>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
       <c r="P201" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>2.116690666560328</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -12179,26 +11903,20 @@
         <v>17</v>
       </c>
       <c r="K202" t="n">
-        <v>0.6192300669665526</v>
+        <v>0.6183973554889365</v>
       </c>
       <c r="L202" t="n">
         <v>30.65353856722748</v>
       </c>
       <c r="M202" t="n">
-        <v>0.9914543051707039</v>
-      </c>
-      <c r="N202" t="n">
-        <v>0.5467863697612891</v>
-      </c>
-      <c r="O202" t="n">
-        <v>0.7691203374659965</v>
-      </c>
+        <v>1.720801904835842</v>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
       <c r="P202" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>19.48853296394216</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -12238,26 +11956,20 @@
         <v>17</v>
       </c>
       <c r="K203" t="n">
-        <v>0.5385163421711662</v>
+        <v>0.5382015538476752</v>
       </c>
       <c r="L203" t="n">
         <v>30.8373427570045</v>
       </c>
       <c r="M203" t="n">
-        <v>1.06923049452409</v>
-      </c>
-      <c r="N203" t="n">
-        <v>0.5467863697612891</v>
-      </c>
-      <c r="O203" t="n">
-        <v>0.8080084321426895</v>
-      </c>
+        <v>1.491482234915091</v>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
       <c r="P203" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>33.3526333700355</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -12297,26 +12009,20 @@
         <v>17</v>
       </c>
       <c r="K204" t="n">
-        <v>0.4522874703617749</v>
+        <v>0.4521278570745698</v>
       </c>
       <c r="L204" t="n">
         <v>31.19558243176516</v>
       </c>
       <c r="M204" t="n">
-        <v>1.187175472566269</v>
-      </c>
-      <c r="N204" t="n">
-        <v>0.5371389694150598</v>
-      </c>
-      <c r="O204" t="n">
-        <v>0.8621572209906645</v>
-      </c>
+        <v>0.9788732688213817</v>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
       <c r="P204" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>47.54002409884446</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -12356,26 +12062,20 @@
         <v>17</v>
       </c>
       <c r="K205" t="n">
-        <v>0.4322579786603727</v>
+        <v>0.4321198345973218</v>
       </c>
       <c r="L205" t="n">
         <v>31.4115927314934</v>
       </c>
       <c r="M205" t="n">
-        <v>1.333556077280552</v>
-      </c>
-      <c r="N205" t="n">
-        <v>0.4468478738436192</v>
-      </c>
-      <c r="O205" t="n">
-        <v>0.8902019755620858</v>
-      </c>
+        <v>0.9788732688213817</v>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
       <c r="P205" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q205" t="n">
-        <v>51.44270732634141</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12415,26 +12115,20 @@
         <v>17</v>
       </c>
       <c r="K206" t="n">
-        <v>0.4041573121506322</v>
+        <v>0.4038849076641726</v>
       </c>
       <c r="L206" t="n">
         <v>31.43494742474523</v>
       </c>
       <c r="M206" t="n">
-        <v>1.333556077280552</v>
-      </c>
-      <c r="N206" t="n">
-        <v>0.4468478738436192</v>
-      </c>
-      <c r="O206" t="n">
-        <v>0.8902019755620858</v>
-      </c>
+        <v>0.9478262599968733</v>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
       <c r="P206" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>54.5993692166947</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12474,26 +12168,20 @@
         <v>17</v>
       </c>
       <c r="K207" t="n">
-        <v>0.4213399913646258</v>
+        <v>0.4218699525635712</v>
       </c>
       <c r="L207" t="n">
         <v>31.74827007106276</v>
       </c>
       <c r="M207" t="n">
-        <v>1.269293198848958</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0.4468478738436192</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0.8580705363462886</v>
-      </c>
+        <v>1.047773289556459</v>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
       <c r="P207" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>50.89681168185607</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12533,26 +12221,20 @@
         <v>17</v>
       </c>
       <c r="K208" t="n">
-        <v>0.470025857502466</v>
+        <v>0.4707722187943567</v>
       </c>
       <c r="L208" t="n">
         <v>31.89387122170205</v>
       </c>
       <c r="M208" t="n">
-        <v>1.167607646918589</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0.3239816099842603</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0.7457946284514246</v>
-      </c>
+        <v>1.047773289556459</v>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
       <c r="P208" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>36.97650270310577</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12592,26 +12274,20 @@
         <v>17</v>
       </c>
       <c r="K209" t="n">
-        <v>0.6684152252175423</v>
+        <v>0.6714789403316066</v>
       </c>
       <c r="L209" t="n">
         <v>32.18557875425769</v>
       </c>
       <c r="M209" t="n">
-        <v>1.058335978988722</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0.161947049349651</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0.6101415141691864</v>
-      </c>
+        <v>1.12276815977813</v>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
       <c r="P209" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>-9.55085167868075</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12651,26 +12327,20 @@
         <v>17</v>
       </c>
       <c r="K210" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.7188562559589849</v>
       </c>
       <c r="L210" t="n">
         <v>32.27311201596218</v>
       </c>
       <c r="M210" t="n">
-        <v>1.058335978988722</v>
-      </c>
-      <c r="N210" t="n">
-        <v>0.161947049349651</v>
-      </c>
-      <c r="O210" t="n">
-        <v>0.6101415141691864</v>
-      </c>
+        <v>1.162272388056961</v>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
       <c r="P210" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>-17.67009935900603</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12710,26 +12380,20 @@
         <v>17</v>
       </c>
       <c r="K211" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.7188562559589849</v>
       </c>
       <c r="L211" t="n">
         <v>32.29527368284402</v>
       </c>
       <c r="M211" t="n">
-        <v>1.058335978988722</v>
-      </c>
-      <c r="N211" t="n">
-        <v>0.161947049349651</v>
-      </c>
-      <c r="O211" t="n">
-        <v>0.6101415141691864</v>
-      </c>
+        <v>1.162272388056961</v>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
       <c r="P211" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>-17.67009935900603</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12769,26 +12433,20 @@
         <v>17</v>
       </c>
       <c r="K212" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.7188562559589849</v>
       </c>
       <c r="L212" t="n">
         <v>32.2954563108531</v>
       </c>
       <c r="M212" t="n">
-        <v>1.058335978988722</v>
-      </c>
-      <c r="N212" t="n">
-        <v>0.161947049349651</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0.6101415141691864</v>
-      </c>
+        <v>1.162272388056961</v>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
       <c r="P212" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>-17.67009935900603</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12828,26 +12486,20 @@
         <v>17</v>
       </c>
       <c r="K213" t="n">
-        <v>0.8504789130187842</v>
+        <v>0.8532998520857752</v>
       </c>
       <c r="L213" t="n">
         <v>32.46520909943512</v>
       </c>
       <c r="M213" t="n">
-        <v>1.072186129913543</v>
-      </c>
-      <c r="N213" t="n">
-        <v>0.1422140172117248</v>
-      </c>
-      <c r="O213" t="n">
-        <v>0.6072000735626337</v>
-      </c>
+        <v>1.430509800817653</v>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
       <c r="P213" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>-40.06568016844219</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12887,26 +12539,20 @@
         <v>17</v>
       </c>
       <c r="K214" t="n">
-        <v>0.8504789130187842</v>
+        <v>0.8532998520857752</v>
       </c>
       <c r="L214" t="n">
         <v>32.46657561323662</v>
       </c>
       <c r="M214" t="n">
-        <v>1.072186129913543</v>
-      </c>
-      <c r="N214" t="n">
-        <v>0.1422140172117248</v>
-      </c>
-      <c r="O214" t="n">
-        <v>0.6072000735626337</v>
-      </c>
+        <v>1.430509800817653</v>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>-40.06568016844219</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12946,26 +12592,20 @@
         <v>17</v>
       </c>
       <c r="K215" t="n">
-        <v>0.902790715459413</v>
+        <v>0.9040520603033265</v>
       </c>
       <c r="L215" t="n">
         <v>32.59853857040257</v>
       </c>
       <c r="M215" t="n">
-        <v>1.072186129913543</v>
-      </c>
-      <c r="N215" t="n">
-        <v>0.1229816940742976</v>
-      </c>
-      <c r="O215" t="n">
-        <v>0.5975839119939201</v>
-      </c>
+        <v>1.430509800817653</v>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
       <c r="P215" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>-51.07346388344504</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -13005,26 +12645,20 @@
         <v>17</v>
       </c>
       <c r="K216" t="n">
-        <v>0.902790715459413</v>
+        <v>0.9040520603033265</v>
       </c>
       <c r="L216" t="n">
         <v>32.60823885576134</v>
       </c>
       <c r="M216" t="n">
-        <v>1.072186129913543</v>
-      </c>
-      <c r="N216" t="n">
-        <v>0.1229816940742976</v>
-      </c>
-      <c r="O216" t="n">
-        <v>0.5975839119939201</v>
-      </c>
+        <v>1.430509800817653</v>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
       <c r="P216" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>-51.07346388344504</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -13064,26 +12698,20 @@
         <v>17</v>
       </c>
       <c r="K217" t="n">
-        <v>0.9315183779958096</v>
+        <v>0.9314095588432793</v>
       </c>
       <c r="L217" t="n">
         <v>32.8104293363669</v>
       </c>
       <c r="M217" t="n">
-        <v>1.104115376478233</v>
-      </c>
-      <c r="N217" t="n">
-        <v>0.09075891683619514</v>
-      </c>
-      <c r="O217" t="n">
-        <v>0.5974371466572139</v>
-      </c>
+        <v>1.430509800817653</v>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
       <c r="P217" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>-55.91905913581876</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -13123,26 +12751,20 @@
         <v>17</v>
       </c>
       <c r="K218" t="n">
-        <v>0.9315183779958096</v>
+        <v>0.9314095588432793</v>
       </c>
       <c r="L218" t="n">
         <v>32.82195910597935</v>
       </c>
       <c r="M218" t="n">
-        <v>1.104115376478233</v>
-      </c>
-      <c r="N218" t="n">
-        <v>0.09075891683619514</v>
-      </c>
-      <c r="O218" t="n">
-        <v>0.5974371466572139</v>
-      </c>
+        <v>1.430509800817653</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
       <c r="P218" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>-55.91905913581876</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13182,13 +12804,13 @@
         <v>17</v>
       </c>
       <c r="K219" t="n">
-        <v>0.8851152668858296</v>
+        <v>0.8844864169514772</v>
       </c>
       <c r="L219" t="n">
         <v>33.09234957516396</v>
       </c>
       <c r="M219" t="n">
-        <v>1.141062351849522</v>
+        <v>1.789005990939995</v>
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
@@ -13235,13 +12857,13 @@
         <v>17</v>
       </c>
       <c r="K220" t="n">
-        <v>0.8426817177160192</v>
+        <v>0.8418695730956948</v>
       </c>
       <c r="L220" t="n">
         <v>33.20210055897164</v>
       </c>
       <c r="M220" t="n">
-        <v>1.191043762367248</v>
+        <v>1.789005990939995</v>
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
@@ -13288,13 +12910,13 @@
         <v>17</v>
       </c>
       <c r="K221" t="n">
-        <v>0.6938713116664846</v>
+        <v>0.6930677684189502</v>
       </c>
       <c r="L221" t="n">
         <v>33.50791465391179</v>
       </c>
       <c r="M221" t="n">
-        <v>1.486028554703088</v>
+        <v>1.77206441721475</v>
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
@@ -13341,13 +12963,13 @@
         <v>17</v>
       </c>
       <c r="K222" t="n">
-        <v>0.6938713116664846</v>
+        <v>0.6930677684189502</v>
       </c>
       <c r="L222" t="n">
         <v>33.53069214196722</v>
       </c>
       <c r="M222" t="n">
-        <v>1.486028554703088</v>
+        <v>1.77206441721475</v>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
@@ -13394,13 +13016,13 @@
         <v>17</v>
       </c>
       <c r="K223" t="n">
-        <v>0.5629841550136426</v>
+        <v>0.5626663577650524</v>
       </c>
       <c r="L223" t="n">
         <v>33.97626225636953</v>
       </c>
       <c r="M223" t="n">
-        <v>1.844475967958824</v>
+        <v>1.395470510692885</v>
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
@@ -13447,13 +13069,13 @@
         <v>17</v>
       </c>
       <c r="K224" t="n">
-        <v>0.5463302263033294</v>
+        <v>0.5461080070969886</v>
       </c>
       <c r="L224" t="n">
         <v>34.00104078212551</v>
       </c>
       <c r="M224" t="n">
-        <v>1.844475967958824</v>
+        <v>1.395470510692885</v>
       </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
@@ -13500,13 +13122,13 @@
         <v>17</v>
       </c>
       <c r="K225" t="n">
-        <v>0.5389585101632535</v>
+        <v>0.5391736064784913</v>
       </c>
       <c r="L225" t="n">
         <v>34.46616989818901</v>
       </c>
       <c r="M225" t="n">
-        <v>1.643774409243683</v>
+        <v>1.195349386467163</v>
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
@@ -13553,13 +13175,13 @@
         <v>17</v>
       </c>
       <c r="K226" t="n">
-        <v>0.552547338455138</v>
+        <v>0.5528163966377017</v>
       </c>
       <c r="L226" t="n">
         <v>34.50962265979545</v>
       </c>
       <c r="M226" t="n">
-        <v>1.555805184715616</v>
+        <v>1.143138415192682</v>
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
@@ -13606,13 +13228,13 @@
         <v>17</v>
       </c>
       <c r="K227" t="n">
-        <v>0.6865475192796013</v>
+        <v>0.6869367356473498</v>
       </c>
       <c r="L227" t="n">
         <v>34.89592355785959</v>
       </c>
       <c r="M227" t="n">
-        <v>1.200149342274758</v>
+        <v>1.127925107555623</v>
       </c>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
@@ -13659,13 +13281,13 @@
         <v>17</v>
       </c>
       <c r="K228" t="n">
-        <v>0.7107101364517812</v>
+        <v>0.7109010806737983</v>
       </c>
       <c r="L228" t="n">
         <v>34.93815401193463</v>
       </c>
       <c r="M228" t="n">
-        <v>1.200149342274758</v>
+        <v>1.128999637704991</v>
       </c>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
@@ -13712,13 +13334,13 @@
         <v>17</v>
       </c>
       <c r="K229" t="n">
-        <v>0.6353390966846304</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="L229" t="n">
         <v>35.34738169592713</v>
       </c>
       <c r="M229" t="n">
-        <v>0.8658938311966332</v>
+        <v>1.006580384496336</v>
       </c>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
@@ -13765,13 +13387,13 @@
         <v>17</v>
       </c>
       <c r="K230" t="n">
-        <v>0.6353390966846304</v>
+        <v>0.6350334582411984</v>
       </c>
       <c r="L230" t="n">
         <v>35.37034443460809</v>
       </c>
       <c r="M230" t="n">
-        <v>0.8658938311966332</v>
+        <v>1.006580384496336</v>
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
@@ -13818,13 +13440,13 @@
         <v>17</v>
       </c>
       <c r="K231" t="n">
-        <v>0.5467863697612891</v>
+        <v>0.5467380705439097</v>
       </c>
       <c r="L231" t="n">
         <v>35.74606603004771</v>
       </c>
       <c r="M231" t="n">
-        <v>0.5385163421711662</v>
+        <v>0.9914318695966965</v>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
@@ -13871,13 +13493,13 @@
         <v>17</v>
       </c>
       <c r="K232" t="n">
-        <v>0.5467863697612891</v>
+        <v>0.5467380705439097</v>
       </c>
       <c r="L232" t="n">
         <v>35.81465331474427</v>
       </c>
       <c r="M232" t="n">
-        <v>0.5385163421711662</v>
+        <v>1.070830314670122</v>
       </c>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
@@ -13924,13 +13546,13 @@
         <v>17</v>
       </c>
       <c r="K233" t="n">
-        <v>0.5296327060372106</v>
+        <v>0.5295971516601461</v>
       </c>
       <c r="L233" t="n">
         <v>35.95770369804295</v>
       </c>
       <c r="M233" t="n">
-        <v>0.5385163421711662</v>
+        <v>1.070830314670122</v>
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
@@ -13977,13 +13599,13 @@
         <v>17</v>
       </c>
       <c r="K234" t="n">
-        <v>0.5371389694150598</v>
+        <v>0.5371396317144246</v>
       </c>
       <c r="L234" t="n">
         <v>36.19280524689942</v>
       </c>
       <c r="M234" t="n">
-        <v>0.4522874703617749</v>
+        <v>1.189002425173676</v>
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
@@ -14030,13 +13652,13 @@
         <v>17</v>
       </c>
       <c r="K235" t="n">
-        <v>0.5292845606250567</v>
+        <v>0.5291850454511349</v>
       </c>
       <c r="L235" t="n">
         <v>36.24248075026841</v>
       </c>
       <c r="M235" t="n">
-        <v>0.4522874703617749</v>
+        <v>1.189002425173676</v>
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
@@ -14083,13 +13705,13 @@
         <v>17</v>
       </c>
       <c r="K236" t="n">
-        <v>0.4468478738436192</v>
+        <v>0.4466851048168524</v>
       </c>
       <c r="L236" t="n">
         <v>36.5664300992254</v>
       </c>
       <c r="M236" t="n">
-        <v>0.4041573121506322</v>
+        <v>1.311819253749365</v>
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
@@ -14136,13 +13758,13 @@
         <v>17</v>
       </c>
       <c r="K237" t="n">
-        <v>0.4468478738436192</v>
+        <v>0.4466851048168524</v>
       </c>
       <c r="L237" t="n">
         <v>36.58981203273922</v>
       </c>
       <c r="M237" t="n">
-        <v>0.4041573121506322</v>
+        <v>1.311819253749365</v>
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
@@ -14189,13 +13811,13 @@
         <v>17</v>
       </c>
       <c r="K238" t="n">
-        <v>0.3239816099842603</v>
+        <v>0.3237822738950355</v>
       </c>
       <c r="L238" t="n">
         <v>36.92267382169684</v>
       </c>
       <c r="M238" t="n">
-        <v>0.470025857502466</v>
+        <v>1.167201635602541</v>
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
@@ -14242,13 +13864,13 @@
         <v>17</v>
       </c>
       <c r="K239" t="n">
-        <v>0.2751216794231886</v>
+        <v>0.2749575999425046</v>
       </c>
       <c r="L239" t="n">
         <v>37.02471651835457</v>
       </c>
       <c r="M239" t="n">
-        <v>0.470025857502466</v>
+        <v>1.167201635602541</v>
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
@@ -14295,13 +13917,13 @@
         <v>17</v>
       </c>
       <c r="K240" t="n">
-        <v>0.161947049349651</v>
+        <v>0.1619014299351722</v>
       </c>
       <c r="L240" t="n">
         <v>37.32948869533178</v>
       </c>
       <c r="M240" t="n">
-        <v>0.7179541259534254</v>
+        <v>1.057776064385731</v>
       </c>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
@@ -14348,13 +13970,13 @@
         <v>17</v>
       </c>
       <c r="K241" t="n">
-        <v>0.1422140172117248</v>
+        <v>0.142177771387514</v>
       </c>
       <c r="L241" t="n">
         <v>37.40431951753322</v>
       </c>
       <c r="M241" t="n">
-        <v>0.8504789130187842</v>
+        <v>1.072418604357054</v>
       </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
@@ -14401,13 +14023,13 @@
         <v>17</v>
       </c>
       <c r="K242" t="n">
-        <v>0.1229816940742976</v>
+        <v>0.1229522451865707</v>
       </c>
       <c r="L242" t="n">
         <v>37.55317844684293</v>
       </c>
       <c r="M242" t="n">
-        <v>0.902790715459413</v>
+        <v>1.072418604357054</v>
       </c>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
@@ -14454,13 +14076,13 @@
         <v>17</v>
       </c>
       <c r="K243" t="n">
-        <v>0.09075891683619514</v>
+        <v>0.09074520326948515</v>
       </c>
       <c r="L243" t="n">
         <v>37.83474241632331</v>
       </c>
       <c r="M243" t="n">
-        <v>0.9315183779958096</v>
+        <v>1.104810542344077</v>
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
@@ -14507,13 +14129,13 @@
         <v>17</v>
       </c>
       <c r="K244" t="n">
-        <v>0.06090024786127952</v>
+        <v>0.06089825857870126</v>
       </c>
       <c r="L244" t="n">
         <v>38.00547640689184</v>
       </c>
       <c r="M244" t="n">
-        <v>0.8851152668858296</v>
+        <v>1.141152858016309</v>
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
